--- a/Documents/Data_Mapping.xlsx
+++ b/Documents/Data_Mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ISEP\ARMDD\ARMDD_1_2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ARMDD_1_2025\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94600313-BEF1-4702-956A-310B608BEE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7F582C-8A9C-4F35-B57F-250617C26AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BD RL" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="279">
   <si>
     <t>Boxes</t>
   </si>
@@ -694,9 +694,6 @@
     <t>DimCostumer</t>
   </si>
   <si>
-    <t>NVARCHAR(1)</t>
-  </si>
-  <si>
     <t>SELECT c.VipCustomer FROM Customers c</t>
   </si>
   <si>
@@ -863,6 +860,9 @@
   </si>
   <si>
     <t>StgArea</t>
+  </si>
+  <si>
+    <t>NVARCHAR(6)</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1276,7 @@
     <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1328,28 +1328,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1364,28 +1358,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="11" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1396,9 +1372,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="12" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1418,15 +1391,32 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="16" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="19" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="11" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="12" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1445,12 +1435,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="12" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2730,17 +2714,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:R46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.265625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -3327,17 +3311,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A5E0C7-DE15-4023-BDFA-96FE8E72E976}">
   <dimension ref="A2:P24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="51.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.86328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16">
@@ -3387,7 +3371,7 @@
       </c>
       <c r="J3" s="30"/>
       <c r="L3" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N3" s="43" t="s">
         <v>98</v>
@@ -3512,7 +3496,7 @@
         <v>55</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J8" s="30"/>
       <c r="L8" s="7" t="s">
@@ -3779,3593 +3763,3794 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA43733-0258-469B-9A5C-4F23F27F8E99}">
-  <dimension ref="B2:Z103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:W103"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.86328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="45.265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.86328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.265625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.1328125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="51.5703125" customWidth="1"/>
+    <col min="21" max="21" width="15.86328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="51.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26">
-      <c r="B2" s="57" t="s">
+    <row r="2" spans="2:23">
+      <c r="B2" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="61" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="72" t="s">
         <v>144</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="64" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="N2" s="79" t="s">
+      <c r="N2" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="82" t="s">
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="84"/>
-      <c r="W2" s="64" t="s">
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="67" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="2:26">
-      <c r="B3" s="69" t="s">
+    <row r="3" spans="2:23">
+      <c r="B3" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="61" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="J3" s="74" t="s">
+      <c r="J3" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="K3" s="75"/>
-      <c r="N3" s="69" t="s">
+      <c r="K3" s="68"/>
+      <c r="N3" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="O3" s="70" t="s">
+      <c r="O3" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="P3" s="70" t="s">
+      <c r="P3" s="61" t="s">
         <v>115</v>
       </c>
-      <c r="Q3" s="70" t="s">
+      <c r="Q3" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="R3" s="71" t="s">
+      <c r="R3" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="S3" s="72" t="s">
+      <c r="S3" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="T3" s="73" t="s">
+      <c r="T3" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="73" t="s">
+      <c r="U3" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="V3" s="74" t="s">
+      <c r="V3" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="W3" s="75"/>
-    </row>
-    <row r="4" spans="2:26">
-      <c r="B4" s="46" t="s">
+      <c r="W3" s="68"/>
+    </row>
+    <row r="4" spans="2:23">
+      <c r="B4" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E4" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H4" s="47" t="s">
+      <c r="E4" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="J4" s="47" t="s">
+      <c r="J4" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="K4" s="65" t="s">
+      <c r="K4" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="M4" s="77"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="45"/>
-      <c r="W4" s="78"/>
-      <c r="X4" s="77"/>
-    </row>
-    <row r="5" spans="2:26">
-      <c r="B5" s="46" t="s">
+      <c r="N4" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O4" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="P4" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q4" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R4" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="S4" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="T4" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="U4" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="V4" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="W4" s="39"/>
+    </row>
+    <row r="5" spans="2:23">
+      <c r="B5" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H5" s="47" t="s">
+      <c r="E5" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="47" t="s">
+      <c r="I5" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="47" t="s">
+      <c r="J5" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="K5" s="65" t="s">
+      <c r="K5" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="M5" s="77"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="78"/>
-      <c r="X5" s="77"/>
-    </row>
-    <row r="6" spans="2:26" ht="45">
-      <c r="B6" s="46" t="s">
+      <c r="N5" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O5" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="P5" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R5" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="S5" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T5" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="U5" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="W5" s="39"/>
+    </row>
+    <row r="6" spans="2:23" ht="42.75">
+      <c r="B6" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E6" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" s="48">
+      <c r="E6" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="47">
         <v>1</v>
       </c>
-      <c r="G6" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H6" s="47" t="s">
+      <c r="G6" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="I6" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="47" t="s">
+      <c r="J6" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K6" s="65" t="s">
+      <c r="K6" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="M6" s="77"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="78"/>
-      <c r="X6" s="77"/>
-    </row>
-    <row r="7" spans="2:26" ht="30">
-      <c r="B7" s="46" t="s">
+      <c r="N6" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O6" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q6" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R6" s="49">
+        <v>2</v>
+      </c>
+      <c r="S6" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T6" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="U6" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="V6" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="W6" s="39"/>
+    </row>
+    <row r="7" spans="2:23" ht="28.5">
+      <c r="B7" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E7" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="48">
+      <c r="E7" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="47">
         <v>1</v>
       </c>
-      <c r="G7" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H7" s="47" t="s">
+      <c r="G7" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="47" t="s">
+      <c r="I7" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="47" t="s">
+      <c r="J7" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K7" s="65" t="s">
+      <c r="K7" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="M7" s="77"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="78"/>
-      <c r="X7" s="77"/>
-    </row>
-    <row r="8" spans="2:26" ht="30">
-      <c r="B8" s="46" t="s">
+      <c r="N7" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O7" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="P7" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q7" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R7" s="49">
+        <v>2</v>
+      </c>
+      <c r="S7" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T7" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="U7" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="V7" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="W7" s="39"/>
+    </row>
+    <row r="8" spans="2:23" ht="28.5">
+      <c r="B8" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="46" t="s">
         <v>211</v>
       </c>
-      <c r="E8" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="48">
+      <c r="E8" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="47">
         <v>1</v>
       </c>
-      <c r="G8" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H8" s="47" t="s">
+      <c r="G8" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="47" t="s">
+      <c r="I8" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="47" t="s">
+      <c r="J8" s="46" t="s">
         <v>211</v>
       </c>
-      <c r="K8" s="65" t="s">
+      <c r="K8" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="M8" s="77"/>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="47"/>
-      <c r="V8" s="47"/>
-      <c r="W8" s="78"/>
-      <c r="X8" s="77"/>
-    </row>
-    <row r="9" spans="2:26">
-      <c r="B9" s="46" t="s">
+      <c r="N8" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O8" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="P8" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q8" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R8" s="49">
+        <v>2</v>
+      </c>
+      <c r="S8" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T8" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="U8" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="V8" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="W8" s="39"/>
+    </row>
+    <row r="9" spans="2:23">
+      <c r="B9" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F9" s="48">
+      <c r="E9" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="47">
         <v>1</v>
       </c>
-      <c r="G9" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H9" s="47" t="s">
+      <c r="G9" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="47" t="s">
+      <c r="I9" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="J9" s="47" t="s">
+      <c r="J9" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="K9" s="65" t="s">
+      <c r="K9" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="M9" s="77"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="47"/>
-      <c r="W9" s="78"/>
-      <c r="X9" s="77"/>
-    </row>
-    <row r="10" spans="2:26" ht="30">
-      <c r="B10" s="46" t="s">
+      <c r="N9" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O9" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q9" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R9" s="49">
+        <v>0</v>
+      </c>
+      <c r="S9" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T9" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="V9" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="W9" s="39"/>
+    </row>
+    <row r="10" spans="2:23" ht="28.5">
+      <c r="B10" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E10" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="48">
+      <c r="E10" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="47">
         <v>2</v>
       </c>
-      <c r="G10" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H10" s="47" t="s">
+      <c r="G10" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H10" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="47" t="s">
+      <c r="I10" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="47" t="s">
+      <c r="J10" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K10" s="65" t="s">
+      <c r="K10" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="M10" s="77"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="78"/>
-      <c r="X10" s="77"/>
-    </row>
-    <row r="11" spans="2:26" ht="30">
-      <c r="B11" s="46" t="s">
+      <c r="N10" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q10" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R10" s="49">
+        <v>1</v>
+      </c>
+      <c r="S10" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T10" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V10" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="W10" s="39"/>
+    </row>
+    <row r="11" spans="2:23" ht="28.5">
+      <c r="B11" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F11" s="48">
+      <c r="E11" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="47">
         <v>2</v>
       </c>
-      <c r="G11" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H11" s="47" t="s">
+      <c r="G11" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H11" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="47" t="s">
+      <c r="J11" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="K11" s="65" t="s">
+      <c r="K11" s="57" t="s">
         <v>161</v>
       </c>
-      <c r="M11" s="77"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="78"/>
-      <c r="X11" s="77"/>
-      <c r="Y11" s="77"/>
-      <c r="Z11" s="77"/>
-    </row>
-    <row r="12" spans="2:26" ht="30">
-      <c r="B12" s="46" t="s">
+      <c r="N11" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O11" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="P11" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q11" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R11" s="49">
+        <v>1</v>
+      </c>
+      <c r="S11" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T11" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="U11" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="V11" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="W11" s="39"/>
+    </row>
+    <row r="12" spans="2:23" ht="28.5">
+      <c r="B12" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F12" s="48">
+      <c r="E12" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="47">
         <v>2</v>
       </c>
-      <c r="G12" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H12" s="47" t="s">
+      <c r="G12" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H12" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="I12" s="47" t="s">
+      <c r="I12" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="47" t="s">
+      <c r="J12" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="K12" s="65" t="s">
+      <c r="K12" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="M12" s="77"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="78"/>
-      <c r="X12" s="77"/>
-    </row>
-    <row r="13" spans="2:26" ht="30">
-      <c r="B13" s="46" t="s">
+      <c r="N12" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O12" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="P12" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q12" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R12" s="49">
+        <v>1</v>
+      </c>
+      <c r="S12" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T12" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="U12" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="W12" s="39"/>
+    </row>
+    <row r="13" spans="2:23" ht="28.5">
+      <c r="B13" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D13" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13" s="48">
+      <c r="E13" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="47">
         <v>2</v>
       </c>
-      <c r="G13" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H13" s="47" t="s">
+      <c r="G13" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H13" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="I13" s="47" t="s">
+      <c r="I13" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="47" t="s">
+      <c r="J13" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="K13" s="65" t="s">
+      <c r="K13" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="M13" s="77"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="78"/>
-      <c r="X13" s="77"/>
-    </row>
-    <row r="14" spans="2:26" ht="30">
-      <c r="B14" s="46" t="s">
+      <c r="N13" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O13" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="P13" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q13" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R13" s="49">
+        <v>1</v>
+      </c>
+      <c r="S13" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="T13" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="U13" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="V13" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="W13" s="39"/>
+    </row>
+    <row r="14" spans="2:23" ht="28.5">
+      <c r="B14" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="D14" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" s="48">
+      <c r="E14" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="47">
         <v>2</v>
       </c>
-      <c r="G14" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H14" s="47" t="s">
+      <c r="G14" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="I14" s="47" t="s">
+      <c r="I14" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="J14" s="47" t="s">
+      <c r="J14" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="K14" s="65" t="s">
+      <c r="K14" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="M14" s="77"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="49"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="52"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="52"/>
-      <c r="W14" s="78"/>
-      <c r="X14" s="77"/>
-    </row>
-    <row r="15" spans="2:26" ht="30">
-      <c r="B15" s="46" t="s">
+      <c r="N14" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O14" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="P14" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q14" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R14" s="49">
+        <v>0</v>
+      </c>
+      <c r="S14" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="T14" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="U14" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="V14" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="W14" s="39"/>
+    </row>
+    <row r="15" spans="2:23" ht="28.5">
+      <c r="B15" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15" s="48">
+      <c r="E15" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="47">
         <v>2</v>
       </c>
-      <c r="G15" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H15" s="47" t="s">
+      <c r="G15" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="I15" s="47" t="s">
+      <c r="I15" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="47" t="s">
+      <c r="J15" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K15" s="65" t="s">
+      <c r="K15" s="57" t="s">
         <v>165</v>
       </c>
-      <c r="M15" s="77"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="52"/>
-      <c r="U15" s="52"/>
-      <c r="V15" s="52"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="77"/>
-    </row>
-    <row r="16" spans="2:26" ht="45">
-      <c r="B16" s="46" t="s">
+      <c r="N15" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O15" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="P15" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q15" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R15" s="49">
+        <v>0</v>
+      </c>
+      <c r="S15" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="T15" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="U15" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="V15" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="W15" s="39"/>
+    </row>
+    <row r="16" spans="2:23" ht="42.75">
+      <c r="B16" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E16" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F16" s="48">
+      <c r="E16" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="47">
         <v>2</v>
       </c>
-      <c r="G16" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H16" s="47" t="s">
+      <c r="G16" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="47" t="s">
+      <c r="I16" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="47" t="s">
+      <c r="J16" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="K16" s="65" t="s">
+      <c r="K16" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="M16" s="77"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="49"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="52"/>
-      <c r="U16" s="52"/>
-      <c r="V16" s="52"/>
-      <c r="W16" s="86"/>
-      <c r="X16" s="77"/>
-    </row>
-    <row r="17" spans="2:24" ht="25.5">
-      <c r="B17" s="46" t="s">
+      <c r="N16" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="O16" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="P16" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q16" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="48">
+        <v>0</v>
+      </c>
+      <c r="S16" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="T16" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="U16" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="V16" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="W16" s="66"/>
+    </row>
+    <row r="17" spans="2:23" ht="25.5">
+      <c r="B17" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="48">
+      <c r="E17" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="47">
         <v>1</v>
       </c>
-      <c r="G17" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H17" s="47" t="s">
+      <c r="G17" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H17" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="I17" s="47" t="s">
+      <c r="I17" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="47" t="s">
+      <c r="J17" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="K17" s="66" t="s">
+      <c r="K17" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="M17" s="77"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="47"/>
-      <c r="V17" s="47"/>
-      <c r="W17" s="78"/>
-      <c r="X17" s="77"/>
-    </row>
-    <row r="18" spans="2:24">
-      <c r="B18" s="46" t="s">
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="39"/>
+    </row>
+    <row r="18" spans="2:23">
+      <c r="B18" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" s="50">
+      <c r="E18" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="49">
         <v>0</v>
       </c>
-      <c r="G18" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I18" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J18" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K18" s="65" t="s">
+      <c r="G18" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K18" s="57" t="s">
         <v>169</v>
       </c>
       <c r="L18" s="37"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="47"/>
-      <c r="O18" s="47"/>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="49"/>
-      <c r="S18" s="49"/>
-      <c r="T18" s="49"/>
-      <c r="U18" s="47"/>
-      <c r="V18" s="47"/>
-      <c r="W18" s="78"/>
-      <c r="X18" s="77"/>
-    </row>
-    <row r="19" spans="2:24">
-      <c r="B19" s="46" t="s">
+      <c r="M18" s="37"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="39"/>
+    </row>
+    <row r="19" spans="2:23">
+      <c r="B19" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="E19" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F19" s="50">
+      <c r="E19" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="49">
         <v>0</v>
       </c>
-      <c r="G19" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H19" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I19" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K19" s="65" t="s">
+      <c r="G19" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K19" s="57" t="s">
         <v>170</v>
       </c>
       <c r="L19" s="38"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="78"/>
-      <c r="X19" s="77"/>
-    </row>
-    <row r="20" spans="2:24">
-      <c r="B20" s="46" t="s">
+      <c r="M19" s="38"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="39"/>
+    </row>
+    <row r="20" spans="2:23">
+      <c r="B20" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E20" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" s="50">
+      <c r="E20" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" s="49">
         <v>0</v>
       </c>
-      <c r="G20" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H20" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I20" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J20" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K20" s="65" t="s">
+      <c r="G20" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K20" s="57" t="s">
         <v>171</v>
       </c>
       <c r="L20" s="38"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="49"/>
-      <c r="S20" s="49"/>
-      <c r="T20" s="49"/>
-      <c r="U20" s="49"/>
-      <c r="V20" s="49"/>
-      <c r="W20" s="78"/>
-      <c r="X20" s="77"/>
-    </row>
-    <row r="21" spans="2:24">
-      <c r="B21" s="46" t="s">
+      <c r="M20" s="38"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="48"/>
+      <c r="W20" s="39"/>
+    </row>
+    <row r="21" spans="2:23">
+      <c r="B21" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E21" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G21" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H21" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J21" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K21" s="65" t="s">
+      <c r="E21" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K21" s="57" t="s">
         <v>123</v>
       </c>
       <c r="L21" s="38"/>
-      <c r="M21" s="85"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="49"/>
-      <c r="S21" s="49"/>
-      <c r="T21" s="49"/>
-      <c r="U21" s="49"/>
-      <c r="V21" s="49"/>
-      <c r="W21" s="78"/>
-    </row>
-    <row r="22" spans="2:24">
-      <c r="B22" s="46" t="s">
+      <c r="M21" s="38"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="48"/>
+      <c r="U21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="39"/>
+    </row>
+    <row r="22" spans="2:23">
+      <c r="B22" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G22" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H22" s="49" t="s">
+      <c r="E22" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G22" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="49" t="s">
+      <c r="I22" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="J22" s="49" t="s">
+      <c r="J22" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="K22" s="65" t="s">
+      <c r="K22" s="57" t="s">
         <v>203</v>
       </c>
       <c r="L22" s="38"/>
-      <c r="M22" s="85"/>
-      <c r="N22" s="47"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="49"/>
-      <c r="S22" s="49"/>
-      <c r="T22" s="49"/>
-      <c r="U22" s="49"/>
-      <c r="V22" s="49"/>
-      <c r="W22" s="78"/>
-    </row>
-    <row r="23" spans="2:24" ht="45">
-      <c r="B23" s="46" t="s">
+      <c r="M22" s="38"/>
+      <c r="N22" s="46"/>
+      <c r="O22" s="46"/>
+      <c r="P22" s="46"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="48"/>
+      <c r="V22" s="48"/>
+      <c r="W22" s="39"/>
+    </row>
+    <row r="23" spans="2:23" ht="42.75">
+      <c r="B23" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F23" s="50">
+      <c r="E23" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" s="49">
         <v>1</v>
       </c>
-      <c r="G23" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H23" s="49" t="s">
+      <c r="G23" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="49" t="s">
+      <c r="I23" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="47" t="s">
+      <c r="J23" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K23" s="65" t="s">
+      <c r="K23" s="57" t="s">
         <v>173</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="38"/>
     </row>
-    <row r="24" spans="2:24">
-      <c r="B24" s="46" t="s">
+    <row r="24" spans="2:23">
+      <c r="B24" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="50">
+      <c r="E24" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="49">
         <v>1</v>
       </c>
-      <c r="G24" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H24" s="49" t="s">
+      <c r="G24" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I24" s="49" t="s">
+      <c r="I24" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="49" t="s">
+      <c r="J24" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="K24" s="65" t="s">
+      <c r="K24" s="57" t="s">
         <v>178</v>
       </c>
       <c r="L24" s="38"/>
       <c r="M24" s="38"/>
     </row>
-    <row r="25" spans="2:24">
-      <c r="B25" s="46" t="s">
+    <row r="25" spans="2:23">
+      <c r="B25" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="47" t="s">
+      <c r="D25" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E25" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F25" s="50">
+      <c r="E25" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="49">
         <v>1</v>
       </c>
-      <c r="G25" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H25" s="49" t="s">
+      <c r="G25" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H25" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I25" s="49" t="s">
+      <c r="I25" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="J25" s="47" t="s">
+      <c r="J25" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K25" s="65" t="s">
+      <c r="K25" s="57" t="s">
         <v>177</v>
       </c>
       <c r="L25" s="38"/>
       <c r="M25" s="38"/>
     </row>
-    <row r="26" spans="2:24" ht="45">
-      <c r="B26" s="46" t="s">
+    <row r="26" spans="2:23" ht="42.75">
+      <c r="B26" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E26" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" s="50">
+      <c r="E26" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="49">
         <v>1</v>
       </c>
-      <c r="G26" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H26" s="49" t="s">
+      <c r="G26" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H26" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I26" s="49" t="s">
+      <c r="I26" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="J26" s="47" t="s">
+      <c r="J26" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K26" s="65" t="s">
+      <c r="K26" s="57" t="s">
         <v>176</v>
       </c>
       <c r="L26" s="38"/>
       <c r="M26" s="38"/>
     </row>
-    <row r="27" spans="2:24">
-      <c r="B27" s="46" t="s">
+    <row r="27" spans="2:23">
+      <c r="B27" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="E27" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F27" s="50">
+      <c r="E27" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="49">
         <v>1</v>
       </c>
-      <c r="G27" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H27" s="49" t="s">
+      <c r="G27" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H27" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I27" s="49" t="s">
+      <c r="I27" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="J27" s="47" t="s">
+      <c r="J27" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="K27" s="65" t="s">
+      <c r="K27" s="57" t="s">
         <v>179</v>
       </c>
       <c r="L27" s="38"/>
       <c r="M27" s="38"/>
     </row>
-    <row r="28" spans="2:24">
-      <c r="B28" s="46" t="s">
+    <row r="28" spans="2:23">
+      <c r="B28" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="47" t="s">
+      <c r="D28" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="E28" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F28" s="50">
+      <c r="E28" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="49">
         <v>1</v>
       </c>
-      <c r="G28" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H28" s="49" t="s">
+      <c r="G28" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H28" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="I28" s="47" t="s">
+      <c r="I28" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="47" t="s">
+      <c r="J28" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="K28" s="66" t="s">
+      <c r="K28" s="58" t="s">
         <v>181</v>
       </c>
       <c r="L28" s="38"/>
       <c r="M28" s="38"/>
     </row>
-    <row r="29" spans="2:24" ht="30">
-      <c r="B29" s="46" t="s">
+    <row r="29" spans="2:23" ht="28.5">
+      <c r="B29" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E29" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F29" s="50">
+      <c r="E29" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F29" s="49">
         <v>2</v>
       </c>
-      <c r="G29" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H29" s="49" t="s">
+      <c r="G29" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H29" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I29" s="49" t="s">
+      <c r="I29" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="J29" s="47" t="s">
+      <c r="J29" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K29" s="65" t="s">
+      <c r="K29" s="57" t="s">
         <v>213</v>
       </c>
       <c r="L29" s="38"/>
       <c r="M29" s="38"/>
     </row>
-    <row r="30" spans="2:24" ht="30">
-      <c r="B30" s="46" t="s">
+    <row r="30" spans="2:23" ht="28.5">
+      <c r="B30" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="47" t="s">
+      <c r="D30" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E30" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F30" s="50">
+      <c r="E30" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" s="49">
         <v>2</v>
       </c>
-      <c r="G30" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H30" s="49" t="s">
+      <c r="G30" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H30" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I30" s="47" t="s">
+      <c r="I30" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="J30" s="47" t="s">
+      <c r="J30" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K30" s="65" t="s">
+      <c r="K30" s="57" t="s">
         <v>214</v>
       </c>
       <c r="L30" s="38"/>
       <c r="M30" s="38"/>
     </row>
-    <row r="31" spans="2:24" ht="30">
-      <c r="B31" s="46" t="s">
+    <row r="31" spans="2:23" ht="28.5">
+      <c r="B31" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="47" t="s">
+      <c r="D31" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E31" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F31" s="50">
+      <c r="E31" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" s="49">
         <v>2</v>
       </c>
-      <c r="G31" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H31" s="49" t="s">
+      <c r="G31" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I31" s="47" t="s">
+      <c r="I31" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="J31" s="47" t="s">
+      <c r="J31" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K31" s="65" t="s">
+      <c r="K31" s="57" t="s">
         <v>215</v>
       </c>
       <c r="L31" s="38"/>
       <c r="M31" s="38"/>
     </row>
-    <row r="32" spans="2:24" ht="30">
-      <c r="B32" s="46" t="s">
+    <row r="32" spans="2:23" ht="28.5">
+      <c r="B32" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="47" t="s">
+      <c r="D32" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E32" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F32" s="50">
+      <c r="E32" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="49">
         <v>2</v>
       </c>
-      <c r="G32" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H32" s="49" t="s">
+      <c r="G32" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H32" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I32" s="47" t="s">
+      <c r="I32" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J32" s="47" t="s">
+      <c r="J32" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K32" s="65" t="s">
+      <c r="K32" s="57" t="s">
         <v>216</v>
       </c>
       <c r="L32" s="38"/>
       <c r="M32" s="38"/>
     </row>
-    <row r="33" spans="2:13" ht="30">
-      <c r="B33" s="46" t="s">
+    <row r="33" spans="2:13" ht="28.5">
+      <c r="B33" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="47" t="s">
+      <c r="D33" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F33" s="50">
+      <c r="E33" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="49">
         <v>2</v>
       </c>
-      <c r="G33" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H33" s="49" t="s">
+      <c r="G33" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H33" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I33" s="47" t="s">
+      <c r="I33" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="J33" s="49" t="s">
+      <c r="J33" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="K33" s="65" t="s">
+      <c r="K33" s="57" t="s">
         <v>217</v>
       </c>
       <c r="L33" s="38"/>
       <c r="M33" s="38"/>
     </row>
-    <row r="34" spans="2:13" ht="30">
-      <c r="B34" s="46" t="s">
+    <row r="34" spans="2:13" ht="28.5">
+      <c r="B34" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="47" t="s">
+      <c r="D34" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F34" s="50">
+      <c r="E34" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="49">
         <v>2</v>
       </c>
-      <c r="G34" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H34" s="49" t="s">
+      <c r="G34" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H34" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I34" s="47" t="s">
+      <c r="I34" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="47" t="s">
+      <c r="J34" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="K34" s="65" t="s">
+      <c r="K34" s="57" t="s">
         <v>218</v>
       </c>
       <c r="L34" s="38"/>
       <c r="M34" s="38"/>
     </row>
-    <row r="35" spans="2:13" ht="30">
-      <c r="B35" s="46" t="s">
+    <row r="35" spans="2:13" ht="28.5">
+      <c r="B35" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E35" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" s="50">
+      <c r="E35" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="49">
         <v>2</v>
       </c>
-      <c r="G35" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H35" s="49" t="s">
+      <c r="G35" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H35" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I35" s="47" t="s">
+      <c r="I35" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="J35" s="47" t="s">
+      <c r="J35" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="K35" s="65" t="s">
+      <c r="K35" s="57" t="s">
         <v>219</v>
       </c>
       <c r="L35" s="38"/>
       <c r="M35" s="38"/>
     </row>
-    <row r="36" spans="2:13" ht="30">
-      <c r="B36" s="46" t="s">
+    <row r="36" spans="2:13" ht="28.5">
+      <c r="B36" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C36" s="47" t="s">
+      <c r="C36" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="47" t="s">
+      <c r="D36" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E36" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F36" s="50">
+      <c r="E36" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="49">
         <v>2</v>
       </c>
-      <c r="G36" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H36" s="49" t="s">
+      <c r="G36" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H36" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I36" s="47" t="s">
+      <c r="I36" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="J36" s="47" t="s">
+      <c r="J36" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K36" s="65" t="s">
+      <c r="K36" s="57" t="s">
         <v>220</v>
       </c>
       <c r="L36" s="38"/>
       <c r="M36" s="38"/>
     </row>
     <row r="37" spans="2:13" ht="32.25" customHeight="1">
-      <c r="B37" s="46" t="s">
+      <c r="B37" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C37" s="47" t="s">
+      <c r="C37" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="47" t="s">
+      <c r="D37" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="E37" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F37" s="50">
+      <c r="E37" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="49">
         <v>2</v>
       </c>
-      <c r="G37" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H37" s="49" t="s">
+      <c r="G37" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H37" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="I37" s="49" t="s">
+      <c r="I37" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="J37" s="49" t="s">
+      <c r="J37" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="K37" s="65" t="s">
+      <c r="K37" s="57" t="s">
         <v>184</v>
       </c>
       <c r="L37" s="38"/>
       <c r="M37" s="38"/>
     </row>
-    <row r="38" spans="2:13" ht="30">
-      <c r="B38" s="46" t="s">
+    <row r="38" spans="2:13" ht="28.5">
+      <c r="B38" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C38" s="47" t="s">
+      <c r="C38" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="47" t="s">
+      <c r="D38" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="E38" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F38" s="50">
+      <c r="E38" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="49">
         <v>2</v>
       </c>
-      <c r="G38" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H38" s="49" t="s">
+      <c r="G38" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H38" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="I38" s="49" t="s">
+      <c r="I38" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="J38" s="49" t="s">
+      <c r="J38" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="K38" s="65" t="s">
+      <c r="K38" s="57" t="s">
         <v>185</v>
       </c>
       <c r="L38" s="38"/>
       <c r="M38" s="38"/>
     </row>
-    <row r="39" spans="2:13" ht="30">
-      <c r="B39" s="46" t="s">
+    <row r="39" spans="2:13" ht="28.5">
+      <c r="B39" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="C39" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="47" t="s">
+      <c r="D39" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E39" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F39" s="50">
+      <c r="E39" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" s="49">
         <v>2</v>
       </c>
-      <c r="G39" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H39" s="49" t="s">
+      <c r="G39" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H39" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="I39" s="49" t="s">
+      <c r="I39" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="J39" s="49" t="s">
+      <c r="J39" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="K39" s="65" t="s">
+      <c r="K39" s="57" t="s">
         <v>186</v>
       </c>
       <c r="L39" s="38"/>
       <c r="M39" s="38"/>
     </row>
     <row r="40" spans="2:13">
-      <c r="B40" s="46" t="s">
+      <c r="B40" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C40" s="47" t="s">
+      <c r="C40" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="47" t="s">
+      <c r="D40" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F40" s="50">
+      <c r="E40" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F40" s="49">
         <v>0</v>
       </c>
-      <c r="G40" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H40" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I40" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J40" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K40" s="65" t="s">
+      <c r="G40" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K40" s="57" t="s">
         <v>169</v>
       </c>
       <c r="L40" s="38"/>
       <c r="M40" s="38"/>
     </row>
     <row r="41" spans="2:13">
-      <c r="B41" s="46" t="s">
+      <c r="B41" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C41" s="47" t="s">
+      <c r="C41" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="47" t="s">
+      <c r="D41" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F41" s="50">
+      <c r="E41" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F41" s="49">
         <v>0</v>
       </c>
-      <c r="G41" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H41" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I41" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J41" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K41" s="65" t="s">
+      <c r="G41" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K41" s="57" t="s">
         <v>170</v>
       </c>
       <c r="L41" s="38"/>
       <c r="M41" s="38"/>
     </row>
     <row r="42" spans="2:13">
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="C42" s="47" t="s">
+      <c r="C42" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="47" t="s">
+      <c r="D42" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E42" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F42" s="50">
+      <c r="E42" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F42" s="49">
         <v>0</v>
       </c>
-      <c r="G42" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H42" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I42" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J42" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K42" s="65" t="s">
+      <c r="G42" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I42" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J42" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K42" s="57" t="s">
         <v>171</v>
       </c>
       <c r="L42" s="38"/>
       <c r="M42" s="38"/>
     </row>
     <row r="43" spans="2:13">
-      <c r="B43" s="46" t="s">
+      <c r="B43" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="47" t="s">
+      <c r="C43" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="47" t="s">
+      <c r="D43" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E43" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F43" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G43" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H43" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I43" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J43" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K43" s="65" t="s">
+      <c r="E43" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G43" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I43" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J43" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K43" s="57" t="s">
         <v>201</v>
       </c>
       <c r="L43" s="38"/>
       <c r="M43" s="38"/>
     </row>
     <row r="44" spans="2:13">
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C44" s="47" t="s">
+      <c r="C44" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="D44" s="47" t="s">
+      <c r="D44" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="50">
+      <c r="E44" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="49">
         <v>0</v>
       </c>
-      <c r="G44" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H44" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I44" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J44" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K44" s="65" t="s">
+      <c r="G44" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I44" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J44" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K44" s="57" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="45" spans="2:13">
-      <c r="B45" s="46" t="s">
+      <c r="B45" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C45" s="47" t="s">
+      <c r="C45" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="D45" s="47" t="s">
+      <c r="D45" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E45" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F45" s="50">
+      <c r="E45" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F45" s="49">
         <v>0</v>
       </c>
-      <c r="G45" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H45" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I45" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J45" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K45" s="65" t="s">
+      <c r="G45" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I45" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J45" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K45" s="57" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="46" spans="2:13">
-      <c r="B46" s="46" t="s">
+      <c r="B46" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C46" s="47" t="s">
+      <c r="C46" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="47" t="s">
+      <c r="D46" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E46" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F46" s="50">
+      <c r="E46" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F46" s="49">
         <v>0</v>
       </c>
-      <c r="G46" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H46" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I46" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J46" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K46" s="65" t="s">
+      <c r="G46" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J46" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K46" s="57" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="47" spans="2:13">
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C47" s="47" t="s">
+      <c r="C47" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="D47" s="47" t="s">
+      <c r="D47" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="E47" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F47" s="50">
+      <c r="E47" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F47" s="49">
         <v>0</v>
       </c>
-      <c r="G47" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H47" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I47" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J47" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K47" s="65" t="s">
+      <c r="G47" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H47" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I47" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J47" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K47" s="57" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="48" spans="2:13">
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D48" s="47" t="s">
+      <c r="D48" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E48" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F48" s="50">
+      <c r="E48" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F48" s="49">
         <v>0</v>
       </c>
-      <c r="G48" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H48" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I48" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J48" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K48" s="65" t="s">
+      <c r="G48" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I48" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J48" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K48" s="57" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="49" spans="2:11">
-      <c r="B49" s="46" t="s">
+      <c r="B49" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C49" s="47" t="s">
+      <c r="C49" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="D49" s="47" t="s">
+      <c r="D49" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E49" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F49" s="50">
+      <c r="E49" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" s="49">
         <v>0</v>
       </c>
-      <c r="G49" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H49" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I49" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J49" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K49" s="65" t="s">
+      <c r="G49" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I49" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K49" s="57" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="50" spans="2:11">
-      <c r="B50" s="46" t="s">
+      <c r="B50" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="C50" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="47" t="s">
+      <c r="D50" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E50" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F50" s="50">
+      <c r="E50" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F50" s="49">
         <v>0</v>
       </c>
-      <c r="G50" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H50" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I50" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J50" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K50" s="65" t="s">
+      <c r="G50" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H50" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I50" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J50" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K50" s="57" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="51" spans="2:11">
-      <c r="B51" s="46" t="s">
+      <c r="B51" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C51" s="47" t="s">
+      <c r="C51" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="D51" s="47" t="s">
+      <c r="D51" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="E51" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F51" s="50">
+      <c r="E51" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F51" s="49">
         <v>0</v>
       </c>
-      <c r="G51" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H51" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I51" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J51" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K51" s="65" t="s">
+      <c r="G51" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H51" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I51" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J51" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K51" s="57" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="52" spans="2:11">
-      <c r="B52" s="46" t="s">
+      <c r="B52" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="C52" s="47" t="s">
+      <c r="C52" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="D52" s="47" t="s">
+      <c r="D52" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E52" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F52" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G52" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H52" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I52" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J52" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K52" s="65" t="s">
+      <c r="E52" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F52" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G52" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H52" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I52" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J52" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K52" s="57" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="53" spans="2:11">
-      <c r="B53" s="46" t="s">
+      <c r="B53" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="C53" s="47" t="s">
+      <c r="C53" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="D53" s="47" t="s">
+      <c r="D53" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="E53" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F53" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G53" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H53" s="49" t="s">
+      <c r="E53" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F53" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G53" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H53" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="I53" s="47" t="s">
+      <c r="I53" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="J53" s="47" t="s">
+      <c r="J53" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="K53" s="65" t="s">
+      <c r="K53" s="57" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="45">
-      <c r="B54" s="46" t="s">
+    <row r="54" spans="2:11" ht="42.75">
+      <c r="B54" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="47" t="s">
+      <c r="C54" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="D54" s="47" t="s">
+      <c r="D54" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="E54" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F54" s="50">
+      <c r="E54" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F54" s="49">
         <v>1</v>
       </c>
-      <c r="G54" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H54" s="49" t="s">
+      <c r="G54" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H54" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="I54" s="47" t="s">
+      <c r="I54" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="J54" s="47" t="s">
+      <c r="J54" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="K54" s="65" t="s">
+      <c r="K54" s="57" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="55" spans="2:11">
-      <c r="B55" s="46" t="s">
+      <c r="B55" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="C55" s="47" t="s">
+      <c r="C55" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="D55" s="47" t="s">
+      <c r="D55" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="E55" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F55" s="50">
+      <c r="E55" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F55" s="49">
         <v>1</v>
       </c>
-      <c r="G55" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H55" s="49" t="s">
+      <c r="G55" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H55" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="I55" s="47" t="s">
+      <c r="I55" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="J55" s="47" t="s">
+      <c r="J55" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="K55" s="65" t="s">
+      <c r="K55" s="57" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="56" spans="2:11">
-      <c r="B56" s="46" t="s">
+      <c r="B56" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="C56" s="47" t="s">
+      <c r="C56" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="D56" s="47" t="s">
+      <c r="D56" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E56" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F56" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G56" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H56" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I56" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J56" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K56" s="65" t="s">
+      <c r="E56" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F56" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G56" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I56" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J56" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K56" s="57" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="57" spans="2:11">
-      <c r="B57" s="46" t="s">
+      <c r="B57" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="47" t="s">
+      <c r="D57" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E57" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F57" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G57" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H57" s="49" t="s">
+      <c r="E57" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F57" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G57" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H57" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I57" s="47" t="s">
+      <c r="I57" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="J57" s="47" t="s">
+      <c r="J57" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="K57" s="65" t="s">
+      <c r="K57" s="57" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" ht="28.5">
+      <c r="B58" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C58" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F58" s="49">
+        <v>2</v>
+      </c>
+      <c r="G58" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H58" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="J58" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="K58" s="57" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" ht="28.5">
+      <c r="B59" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="E59" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F59" s="49">
+        <v>2</v>
+      </c>
+      <c r="G59" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H59" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I59" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="J59" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="K59" s="57" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" ht="28.5">
+      <c r="B60" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="D60" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E60" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F60" s="49">
+        <v>2</v>
+      </c>
+      <c r="G60" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H60" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I60" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="J60" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="K60" s="57" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C61" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="E61" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F61" s="49">
+        <v>0</v>
+      </c>
+      <c r="G61" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H61" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="I61" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="J61" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="K61" s="57" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
+      <c r="B62" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C62" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="E62" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F62" s="49">
+        <v>1</v>
+      </c>
+      <c r="G62" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H62" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="K62" s="57" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E63" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F63" s="49">
+        <v>1</v>
+      </c>
+      <c r="G63" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H63" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="I63" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="J63" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="K63" s="57" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C64" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="E64" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F64" s="49">
+        <v>1</v>
+      </c>
+      <c r="G64" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H64" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="I64" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="J64" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="K64" s="57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D65" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E65" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F65" s="49">
+        <v>1</v>
+      </c>
+      <c r="G65" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H65" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="I65" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="J65" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="K65" s="57" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C66" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="E66" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F66" s="49">
+        <v>0</v>
+      </c>
+      <c r="G66" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H66" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I66" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J66" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K66" s="57" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C67" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="E67" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F67" s="49">
+        <v>0</v>
+      </c>
+      <c r="G67" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H67" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I67" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J67" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K67" s="57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C68" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D68" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E68" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F68" s="48">
+        <v>0</v>
+      </c>
+      <c r="G68" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="H68" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I68" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J68" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K68" s="57" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="B69" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C69" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="D69" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E69" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G69" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="H69" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J69" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K69" s="57" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="B70" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C70" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="D70" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E70" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F70" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G70" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="H70" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I70" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J70" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K70" s="57"/>
+    </row>
+    <row r="71" spans="2:11" ht="28.5">
+      <c r="B71" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="D71" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="E71" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F71" s="48">
+        <v>2</v>
+      </c>
+      <c r="G71" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="H71" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I71" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="K71" s="57" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C72" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D72" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="E72" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F72" s="48">
+        <v>2</v>
+      </c>
+      <c r="G72" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="H72" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I72" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="J72" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="K72" s="57" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" ht="28.5">
+      <c r="B73" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C73" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="D73" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E73" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F73" s="49">
+        <v>2</v>
+      </c>
+      <c r="G73" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H73" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I73" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="J73" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="K73" s="57" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C74" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="E74" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F74" s="49">
+        <v>2</v>
+      </c>
+      <c r="G74" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H74" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I74" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="J74" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="K74" s="57" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="58" spans="2:11" ht="45">
-      <c r="B58" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C58" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" s="47" t="s">
+    <row r="75" spans="2:11">
+      <c r="B75" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C75" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="D75" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="E58" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F58" s="50">
+      <c r="E75" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F75" s="49">
         <v>2</v>
       </c>
-      <c r="G58" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H58" s="49" t="s">
+      <c r="G75" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H75" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I75" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="J75" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="K75" s="57" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C76" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="E76" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F76" s="49">
         <v>2</v>
       </c>
-      <c r="I58" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="J58" s="47" t="s">
+      <c r="G76" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H76" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="J76" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="K58" s="65" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11" ht="45">
-      <c r="B59" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C59" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="D59" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="E59" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F59" s="50">
+      <c r="K76" s="57" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" s="46" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F77" s="49">
         <v>2</v>
       </c>
-      <c r="G59" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H59" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="I59" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="J59" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="K59" s="65" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11" ht="45">
-      <c r="B60" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C60" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D60" s="47" t="s">
+      <c r="G77" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H77" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I77" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="J77" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="K77" s="57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C78" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="D78" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E78" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F78" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G78" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H78" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I78" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J78" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K78" s="57" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C79" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D79" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E79" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G79" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H79" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I79" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="J79" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="K79" s="57" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" ht="42.75">
+      <c r="B80" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C80" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D80" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="E80" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F80" s="49">
+        <v>1</v>
+      </c>
+      <c r="G80" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H80" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="K80" s="57" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" ht="42.75">
+      <c r="B81" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="D81" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F81" s="49">
+        <v>1</v>
+      </c>
+      <c r="G81" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H81" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="J81" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="K81" s="57" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C82" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="D82" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="E60" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F60" s="50">
-        <v>2</v>
-      </c>
-      <c r="G60" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H60" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="I60" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="J60" s="47" t="s">
+      <c r="E82" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F82" s="49">
+        <v>1</v>
+      </c>
+      <c r="G82" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H82" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="J82" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="K60" s="65" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C61" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="D61" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="E61" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F61" s="50">
-        <v>0</v>
-      </c>
-      <c r="G61" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H61" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="I61" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="J61" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="K61" s="65" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C62" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="D62" s="47" t="s">
-        <v>222</v>
-      </c>
-      <c r="E62" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F62" s="50">
+      <c r="K82" s="57" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C83" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D83" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E83" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F83" s="49">
         <v>1</v>
       </c>
-      <c r="G62" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H62" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="J62" s="47" t="s">
-        <v>222</v>
-      </c>
-      <c r="K62" s="65" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C63" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D63" s="47" t="s">
+      <c r="G83" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H83" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J83" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E63" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F63" s="50">
+      <c r="K83" s="57" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C84" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D84" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E84" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F84" s="49">
         <v>1</v>
       </c>
-      <c r="G63" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H63" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="I63" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="J63" s="47" t="s">
+      <c r="G84" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H84" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I84" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J84" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="K63" s="65" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C64" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="D64" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="E64" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F64" s="50">
-        <v>1</v>
-      </c>
-      <c r="G64" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H64" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="I64" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="J64" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="K64" s="65" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C65" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="D65" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="E65" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F65" s="50">
-        <v>1</v>
-      </c>
-      <c r="G65" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H65" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="I65" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="J65" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="K65" s="65" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C66" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="D66" s="47" t="s">
+      <c r="K84" s="57" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" ht="28.5">
+      <c r="B85" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C85" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D85" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="E66" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F66" s="50">
-        <v>0</v>
-      </c>
-      <c r="G66" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H66" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I66" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J66" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K66" s="65" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C67" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="47" t="s">
+      <c r="E85" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F85" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G85" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H85" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I85" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="J85" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="E67" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F67" s="50">
-        <v>0</v>
-      </c>
-      <c r="G67" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H67" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I67" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J67" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K67" s="65" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C68" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D68" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="E68" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F68" s="49">
-        <v>0</v>
-      </c>
-      <c r="G68" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="H68" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I68" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J68" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K68" s="65" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C69" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="D69" s="47" t="s">
+      <c r="K85" s="57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D86" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E69" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F69" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="G69" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="H69" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I69" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J69" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K69" s="65" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
-      <c r="B70" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C70" s="47" t="s">
+      <c r="E86" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F86" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G86" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H86" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I86" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="J86" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="K86" s="57" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="D87" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E87" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F87" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G87" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H87" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="I87" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="J87" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="K87" s="57" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="D88" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E88" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F88" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G88" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H88" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I88" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="J88" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="K88" s="57" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="D89" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="E89" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F89" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G89" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H89" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="J89" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="K89" s="57" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C90" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="D90" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="E90" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F90" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G90" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H90" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="I90" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="J90" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="K90" s="57" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C91" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="D91" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="E91" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F91" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G91" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H91" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="I91" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="J91" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="K91" s="57" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="D92" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="E92" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F92" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G92" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H92" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="I92" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="J92" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="K92" s="57" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="E93" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F93" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G93" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H93" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="I93" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="J93" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="K93" s="57" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C94" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="D94" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E94" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F94" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G94" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H94" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="I94" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="J94" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="K94" s="57" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" ht="30" customHeight="1">
+      <c r="B95" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C95" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D95" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E95" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F95" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G95" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H95" s="48" t="s">
+        <v>250</v>
+      </c>
+      <c r="I95" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="J95" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="K95" s="57" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" ht="42.75">
+      <c r="B96" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C96" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D96" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E96" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F96" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G96" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H96" s="48" t="s">
+        <v>250</v>
+      </c>
+      <c r="I96" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="J96" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="K96" s="57" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" ht="42.75">
+      <c r="B97" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C97" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="D97" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E97" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F97" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G97" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H97" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="I97" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="J97" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="K97" s="57" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" ht="85.5">
+      <c r="B98" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C98" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D98" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E98" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F98" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G98" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H98" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="I98" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J98" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K98" s="57" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11" ht="128.25">
+      <c r="B99" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C99" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="D99" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E99" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F99" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G99" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="H99" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I99" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J99" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K99" s="57" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" ht="28.5">
+      <c r="B100" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C100" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D100" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E100" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F100" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G100" s="54" t="s">
         <v>277</v>
       </c>
-      <c r="D70" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F70" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="G70" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="H70" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I70" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J70" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K70" s="65"/>
-    </row>
-    <row r="71" spans="2:11" ht="30">
-      <c r="B71" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C71" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="D71" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="E71" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F71" s="49">
-        <v>2</v>
-      </c>
-      <c r="G71" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="H71" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="I71" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="J71" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="K71" s="65" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C72" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="D72" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="E72" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F72" s="49">
-        <v>2</v>
-      </c>
-      <c r="G72" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="H72" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="I72" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="J72" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="K72" s="65" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" ht="30">
-      <c r="B73" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C73" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D73" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="E73" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F73" s="50">
-        <v>2</v>
-      </c>
-      <c r="G73" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H73" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="I73" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="J73" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="K73" s="65" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C74" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="D74" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="E74" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F74" s="50">
-        <v>2</v>
-      </c>
-      <c r="G74" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H74" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="I74" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="J74" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="K74" s="65" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C75" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D75" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="E75" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F75" s="50">
-        <v>2</v>
-      </c>
-      <c r="G75" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H75" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="I75" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="J75" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="K75" s="65" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C76" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="D76" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="E76" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F76" s="50">
-        <v>2</v>
-      </c>
-      <c r="G76" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H76" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="J76" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="K76" s="65" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" ht="30">
-      <c r="B77" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C77" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="D77" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="E77" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F77" s="50">
-        <v>2</v>
-      </c>
-      <c r="G77" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H77" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="I77" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="J77" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="K77" s="65" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="C78" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="D78" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E78" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F78" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="G78" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="H78" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="I78" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J78" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K78" s="65" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="C79" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="D79" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E79" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F79" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="G79" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H79" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="I79" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="J79" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="K79" s="65" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" ht="45">
-      <c r="B80" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="C80" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="D80" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="E80" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F80" s="50">
-        <v>1</v>
-      </c>
-      <c r="G80" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H80" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="I80" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="J80" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="K80" s="65" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11" ht="45">
-      <c r="B81" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="C81" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="D81" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="E81" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F81" s="50">
-        <v>1</v>
-      </c>
-      <c r="G81" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H81" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="I81" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="J81" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="K81" s="65" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="C82" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="D82" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="E82" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F82" s="50">
-        <v>1</v>
-      </c>
-      <c r="G82" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H82" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="I82" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="J82" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="K82" s="65" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="B83" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="C83" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="D83" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E83" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F83" s="50">
-        <v>1</v>
-      </c>
-      <c r="G83" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H83" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="I83" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="J83" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="K83" s="65" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="C84" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="D84" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E84" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F84" s="50">
-        <v>1</v>
-      </c>
-      <c r="G84" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H84" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="I84" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="J84" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="K84" s="65" t="s">
+      <c r="H100" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="I100" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="J100" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="K100" s="57" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
+      <c r="B101" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C101" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="D101" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="E101" s="46" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="85" spans="2:11" ht="30">
-      <c r="B85" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C85" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D85" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E85" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F85" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G85" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H85" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="I85" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="J85" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="K85" s="65" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" s="47" t="s">
-        <v>94</v>
-      </c>
-      <c r="D86" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E86" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F86" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G86" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H86" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="I86" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="J86" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="K86" s="65" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C87" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="D87" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E87" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F87" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G87" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H87" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="I87" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="J87" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="K87" s="65" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11">
-      <c r="B88" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C88" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="D88" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E88" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F88" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G88" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H88" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="I88" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="J88" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="K88" s="65" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C89" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D89" s="47" t="s">
+      <c r="F101" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G101" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="H101" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="I101" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="J101" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="E89" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F89" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G89" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H89" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="J89" s="49" t="s">
+      <c r="K101" s="57" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
+      <c r="B102" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="D102" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="K89" s="65" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
-      <c r="B90" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C90" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="D90" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E90" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F90" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G90" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H90" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="I90" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="J90" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="K90" s="65" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="B91" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C91" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="D91" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E91" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F91" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G91" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H91" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="I91" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="J91" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="K91" s="65" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
-      <c r="B92" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C92" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="D92" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E92" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F92" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G92" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H92" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="I92" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="J92" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="K92" s="65" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
-      <c r="B93" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C93" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="D93" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E93" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F93" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G93" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H93" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="I93" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="J93" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="K93" s="65" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C94" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="D94" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="E94" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F94" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G94" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H94" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="I94" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="J94" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="K94" s="65" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11" ht="30" customHeight="1">
-      <c r="B95" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C95" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="D95" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="E95" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F95" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G95" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H95" s="49" t="s">
-        <v>251</v>
-      </c>
-      <c r="I95" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="J95" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="K95" s="65" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11" ht="45">
-      <c r="B96" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C96" s="47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D96" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="E96" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F96" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G96" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H96" s="49" t="s">
-        <v>251</v>
-      </c>
-      <c r="I96" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="J96" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="K96" s="65" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11" ht="45">
-      <c r="B97" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C97" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="D97" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="E97" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F97" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G97" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H97" s="47" t="s">
-        <v>252</v>
-      </c>
-      <c r="I97" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="J97" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="K97" s="65" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11" ht="90">
-      <c r="B98" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C98" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="D98" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="E98" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F98" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G98" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H98" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="I98" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J98" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K98" s="65" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11" ht="150">
-      <c r="B99" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C99" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="D99" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="E99" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F99" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G99" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="H99" s="49" t="s">
-        <v>268</v>
-      </c>
-      <c r="I99" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="J99" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="K99" s="65" t="s">
+      <c r="E102" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F102" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G102" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="H102" s="46" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="100" spans="2:11" ht="30">
-      <c r="B100" s="46" t="s">
+      <c r="I102" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="J102" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="K102" s="57" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="C100" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D100" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E100" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F100" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G100" s="56" t="s">
-        <v>278</v>
-      </c>
-      <c r="H100" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="I100" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="J100" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="K100" s="65" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11" ht="30">
-      <c r="B101" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C101" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="D101" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="E101" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F101" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G101" s="56" t="s">
-        <v>278</v>
-      </c>
-      <c r="H101" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="I101" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="J101" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="K101" s="65" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11">
-      <c r="B102" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="C102" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="D102" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="E102" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="F102" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G102" s="56" t="s">
-        <v>278</v>
-      </c>
-      <c r="H102" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="I102" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="J102" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="K102" s="65" t="s">
+      <c r="C103" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="D103" s="52" t="s">
+        <v>275</v>
+      </c>
+      <c r="E103" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="F103" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="G103" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="H103" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="I103" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="J103" s="52" t="s">
+        <v>275</v>
+      </c>
+      <c r="K103" s="59" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11">
-      <c r="B103" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="C103" s="54" t="s">
-        <v>198</v>
-      </c>
-      <c r="D103" s="54" t="s">
-        <v>276</v>
-      </c>
-      <c r="E103" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="F103" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="G103" s="63" t="s">
-        <v>278</v>
-      </c>
-      <c r="H103" s="54" t="s">
-        <v>270</v>
-      </c>
-      <c r="I103" s="54" t="s">
-        <v>198</v>
-      </c>
-      <c r="J103" s="54" t="s">
-        <v>276</v>
-      </c>
-      <c r="K103" s="67" t="s">
-        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/Data_Mapping.xlsx
+++ b/Documents/Data_Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ARMDD_1_2025\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7F582C-8A9C-4F35-B57F-250617C26AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB205C9-66B3-4EAF-A08A-23F524FDC80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BD RL" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="273">
   <si>
     <t>Boxes</t>
   </si>
@@ -409,45 +409,24 @@
     <t>Year</t>
   </si>
   <si>
-    <t>YEAR(FullDate)</t>
-  </si>
-  <si>
     <t>Month</t>
   </si>
   <si>
-    <t>MONTH(FullDate)</t>
-  </si>
-  <si>
     <t>MonthName</t>
   </si>
   <si>
-    <t>DATENAME(MONTH, FullDate)</t>
-  </si>
-  <si>
     <t>Quarter</t>
   </si>
   <si>
-    <t>DATEPART(QUARTER, FullDate)</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
-    <t>DAY(FullDate)</t>
-  </si>
-  <si>
     <t>DayOfWeek</t>
   </si>
   <si>
-    <t>DATEPART(WEEKDAY, FullDate)</t>
-  </si>
-  <si>
     <t>DayName</t>
   </si>
   <si>
-    <t>DATENAME(WEEKDAY, FullDate)</t>
-  </si>
-  <si>
     <t>Season</t>
   </si>
   <si>
@@ -863,13 +842,16 @@
   </si>
   <si>
     <t>NVARCHAR(6)</t>
+  </si>
+  <si>
+    <t>NCHAR(7)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -903,6 +885,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="25">
@@ -1276,7 +1266,7 @@
     <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1391,9 +1381,6 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="16" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1436,6 +1423,34 @@
     <xf numFmtId="0" fontId="3" fillId="24" borderId="12" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="60% - Cor1" xfId="2" builtinId="32"/>
@@ -2714,17 +2729,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:R46"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="8" max="8" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -3311,17 +3326,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A5E0C7-DE15-4023-BDFA-96FE8E72E976}">
   <dimension ref="A2:P24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="5" max="5" width="17.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="51.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.86328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16">
@@ -3350,7 +3365,7 @@
         <v>119</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -3371,13 +3386,13 @@
       </c>
       <c r="J3" s="30"/>
       <c r="L3" s="7" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="N3" s="43" t="s">
         <v>98</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -3455,7 +3470,7 @@
         <v>76</v>
       </c>
       <c r="N6" s="43" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="P6" s="24" t="s">
         <v>50</v>
@@ -3479,7 +3494,7 @@
         <v>77</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="P7" s="40" t="s">
         <v>66</v>
@@ -3496,14 +3511,14 @@
         <v>55</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J8" s="30"/>
       <c r="L8" s="7" t="s">
         <v>78</v>
       </c>
       <c r="N8" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P8" s="40" t="s">
         <v>67</v>
@@ -3527,7 +3542,7 @@
         <v>79</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P9" s="40" t="s">
         <v>68</v>
@@ -3548,7 +3563,7 @@
       </c>
       <c r="J10" s="30"/>
       <c r="N10" s="43" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="P10" s="42" t="s">
         <v>69</v>
@@ -3569,7 +3584,7 @@
       </c>
       <c r="J11" s="30"/>
       <c r="N11" s="43" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3589,7 +3604,7 @@
         <v>103</v>
       </c>
       <c r="N12" s="43" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3609,7 +3624,7 @@
         <v>104</v>
       </c>
       <c r="N13" s="43" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3629,7 +3644,7 @@
         <v>105</v>
       </c>
       <c r="N14" s="43" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3649,7 +3664,7 @@
         <v>108</v>
       </c>
       <c r="N15" s="43" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3666,7 +3681,7 @@
         <v>110</v>
       </c>
       <c r="N16" s="43" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -3683,7 +3698,7 @@
         <v>112</v>
       </c>
       <c r="N17" s="43" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -3694,7 +3709,7 @@
         <v>41</v>
       </c>
       <c r="N18" s="43" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -3705,7 +3720,7 @@
         <v>90</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -3721,7 +3736,7 @@
         <v>50</v>
       </c>
       <c r="I21" s="44" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -3729,7 +3744,7 @@
         <v>92</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -3737,7 +3752,7 @@
         <v>88</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -3763,70 +3778,70 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA43733-0258-469B-9A5C-4F23F27F8E99}">
-  <dimension ref="B2:W103"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="B2:W104"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.1328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.86328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45.265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.86328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="45.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.86328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.1328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.86328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="51.59765625" customWidth="1"/>
+    <col min="21" max="21" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="51.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:23">
-      <c r="B2" s="69" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="72" t="s">
-        <v>144</v>
-      </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="67" t="s">
+      <c r="B2" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="N2" s="75" t="s">
-        <v>141</v>
-      </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="78" t="s">
-        <v>144</v>
-      </c>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="67" t="s">
+      <c r="N2" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="77" t="s">
+        <v>137</v>
+      </c>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="66" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="3" spans="2:23">
       <c r="B3" s="60" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C3" s="61" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D3" s="61" t="s">
         <v>115</v>
@@ -3838,23 +3853,23 @@
         <v>117</v>
       </c>
       <c r="G3" s="63" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H3" s="64" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I3" s="64" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="J3" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="K3" s="68"/>
+      <c r="K3" s="67"/>
       <c r="N3" s="60" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="O3" s="61" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="P3" s="61" t="s">
         <v>115</v>
@@ -3866,22 +3881,22 @@
         <v>117</v>
       </c>
       <c r="S3" s="63" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="T3" s="64" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="U3" s="64" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="V3" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="W3" s="68"/>
+      <c r="W3" s="67"/>
     </row>
     <row r="4" spans="2:23">
       <c r="B4" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C4" s="46" t="s">
         <v>83</v>
@@ -3893,10 +3908,10 @@
         <v>121</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H4" s="46" t="s">
         <v>122</v>
@@ -3908,40 +3923,42 @@
         <v>122</v>
       </c>
       <c r="K4" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="N4" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O4" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="P4" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="N4" s="83" t="s">
+        <v>139</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="Q4" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R4" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="S4" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="T4" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="U4" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="V4" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="W4" s="39"/>
+      <c r="Q4" s="84" t="s">
+        <v>121</v>
+      </c>
+      <c r="R4" s="85" t="s">
+        <v>145</v>
+      </c>
+      <c r="S4" s="85" t="s">
+        <v>145</v>
+      </c>
+      <c r="T4" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="U4" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="V4" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="W4" s="86" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="5" spans="2:23">
       <c r="B5" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C5" s="46" t="s">
         <v>42</v>
@@ -3953,10 +3970,10 @@
         <v>121</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H5" s="46" t="s">
         <v>8</v>
@@ -3965,49 +3982,51 @@
         <v>42</v>
       </c>
       <c r="J5" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="K5" s="57" t="s">
-        <v>155</v>
-      </c>
       <c r="N5" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O5" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="P5" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="O5" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="Q5" s="46" t="s">
+      <c r="Q5" s="80" t="s">
         <v>121</v>
       </c>
       <c r="R5" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="S5" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T5" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="U5" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="V5" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="W5" s="39"/>
-    </row>
-    <row r="6" spans="2:23" ht="42.75">
+        <v>145</v>
+      </c>
+      <c r="S5" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T5" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="U5" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" s="80" t="s">
+        <v>141</v>
+      </c>
+      <c r="W5" s="57" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" ht="45">
       <c r="B6" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C6" s="48" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>121</v>
@@ -4016,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H6" s="46" t="s">
         <v>8</v>
@@ -4025,49 +4044,51 @@
         <v>43</v>
       </c>
       <c r="J6" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K6" s="57" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="N6" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O6" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="P6" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q6" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R6" s="49">
-        <v>2</v>
-      </c>
-      <c r="S6" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T6" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="U6" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="V6" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="W6" s="39"/>
-    </row>
-    <row r="7" spans="2:23" ht="28.5">
+        <v>139</v>
+      </c>
+      <c r="O6" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q6" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R6" s="47">
+        <v>1</v>
+      </c>
+      <c r="S6" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T6" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="U6" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="V6" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="W6" s="57" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" ht="30">
       <c r="B7" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C7" s="46" t="s">
         <v>81</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>121</v>
@@ -4076,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H7" s="46" t="s">
         <v>1</v>
@@ -4085,49 +4106,51 @@
         <v>23</v>
       </c>
       <c r="J7" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K7" s="57" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="N7" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O7" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="P7" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q7" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R7" s="49">
-        <v>2</v>
-      </c>
-      <c r="S7" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T7" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="U7" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="V7" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="W7" s="39"/>
-    </row>
-    <row r="8" spans="2:23" ht="28.5">
+        <v>139</v>
+      </c>
+      <c r="O7" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="P7" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q7" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R7" s="47">
+        <v>1</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T7" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="V7" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="W7" s="57" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" ht="30">
       <c r="B8" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C8" s="46" t="s">
         <v>82</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="E8" s="46" t="s">
         <v>121</v>
@@ -4136,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H8" s="46" t="s">
         <v>1</v>
@@ -4145,49 +4168,51 @@
         <v>24</v>
       </c>
       <c r="J8" s="46" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K8" s="57" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="N8" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O8" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="P8" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q8" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R8" s="49">
-        <v>2</v>
-      </c>
-      <c r="S8" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T8" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="U8" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="V8" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="W8" s="39"/>
+        <v>139</v>
+      </c>
+      <c r="O8" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" s="80" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q8" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R8" s="47">
+        <v>1</v>
+      </c>
+      <c r="S8" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T8" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="W8" s="57" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="9" spans="2:23">
       <c r="B9" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C9" s="46" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E9" s="46" t="s">
         <v>121</v>
@@ -4196,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H9" s="46" t="s">
         <v>8</v>
@@ -4205,49 +4230,51 @@
         <v>44</v>
       </c>
       <c r="J9" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="K9" s="57" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="N9" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O9" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="P9" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q9" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R9" s="49">
-        <v>0</v>
-      </c>
-      <c r="S9" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T9" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="U9" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="V9" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="W9" s="39"/>
-    </row>
-    <row r="10" spans="2:23" ht="28.5">
+        <v>139</v>
+      </c>
+      <c r="O9" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9" s="80" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q9" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R9" s="47">
+        <v>1</v>
+      </c>
+      <c r="S9" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T9" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="U9" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="V9" s="80" t="s">
+        <v>143</v>
+      </c>
+      <c r="W9" s="57" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" ht="30">
       <c r="B10" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C10" s="46" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E10" s="46" t="s">
         <v>121</v>
@@ -4256,7 +4283,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H10" s="46" t="s">
         <v>0</v>
@@ -4265,49 +4292,51 @@
         <v>14</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K10" s="57" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="N10" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O10" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="P10" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R10" s="49">
-        <v>1</v>
-      </c>
-      <c r="S10" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T10" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="U10" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="V10" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="W10" s="39"/>
-    </row>
-    <row r="11" spans="2:23" ht="28.5">
+        <v>139</v>
+      </c>
+      <c r="O10" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="P10" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q10" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R10" s="47">
+        <v>2</v>
+      </c>
+      <c r="S10" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T10" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="U10" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="V10" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="W10" s="57" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23" ht="30">
       <c r="B11" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C11" s="46" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E11" s="46" t="s">
         <v>121</v>
@@ -4316,7 +4345,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H11" s="46" t="s">
         <v>0</v>
@@ -4325,49 +4354,51 @@
         <v>15</v>
       </c>
       <c r="J11" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K11" s="57" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N11" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O11" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="P11" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q11" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R11" s="49">
-        <v>1</v>
-      </c>
-      <c r="S11" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T11" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="U11" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="V11" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="W11" s="39"/>
-    </row>
-    <row r="12" spans="2:23" ht="28.5">
+        <v>139</v>
+      </c>
+      <c r="O11" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="P11" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q11" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R11" s="47">
+        <v>2</v>
+      </c>
+      <c r="S11" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T11" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="U11" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="V11" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="W11" s="57" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" ht="30">
       <c r="B12" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C12" s="46" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E12" s="46" t="s">
         <v>121</v>
@@ -4376,7 +4407,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H12" s="46" t="s">
         <v>0</v>
@@ -4385,49 +4416,51 @@
         <v>16</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K12" s="57" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N12" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O12" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="P12" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q12" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R12" s="49">
-        <v>1</v>
-      </c>
-      <c r="S12" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T12" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="U12" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="V12" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="W12" s="39"/>
-    </row>
-    <row r="13" spans="2:23" ht="28.5">
+        <v>139</v>
+      </c>
+      <c r="O12" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q12" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R12" s="47">
+        <v>2</v>
+      </c>
+      <c r="S12" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T12" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="U12" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="V12" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="W12" s="57" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23" ht="30">
       <c r="B13" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C13" s="46" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E13" s="46" t="s">
         <v>121</v>
@@ -4436,7 +4469,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H13" s="46" t="s">
         <v>0</v>
@@ -4445,49 +4478,51 @@
         <v>17</v>
       </c>
       <c r="J13" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K13" s="57" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="N13" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O13" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="P13" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q13" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R13" s="49">
-        <v>1</v>
-      </c>
-      <c r="S13" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="T13" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="U13" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="V13" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="W13" s="39"/>
-    </row>
-    <row r="14" spans="2:23" ht="28.5">
+        <v>139</v>
+      </c>
+      <c r="O13" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="P13" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q13" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R13" s="47">
+        <v>2</v>
+      </c>
+      <c r="S13" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T13" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="U13" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="V13" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="W13" s="57" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" ht="30">
       <c r="B14" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C14" s="46" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E14" s="46" t="s">
         <v>121</v>
@@ -4496,58 +4531,60 @@
         <v>2</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H14" s="46" t="s">
         <v>0</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K14" s="57" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="N14" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O14" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="P14" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q14" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R14" s="49">
+        <v>139</v>
+      </c>
+      <c r="O14" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="P14" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q14" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R14" s="47">
+        <v>2</v>
+      </c>
+      <c r="S14" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T14" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="S14" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="T14" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="U14" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="V14" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="W14" s="39"/>
-    </row>
-    <row r="15" spans="2:23" ht="28.5">
+      <c r="U14" s="80" t="s">
+        <v>146</v>
+      </c>
+      <c r="V14" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="W14" s="57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23" ht="30">
       <c r="B15" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C15" s="46" t="s">
         <v>84</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E15" s="46" t="s">
         <v>121</v>
@@ -4556,7 +4593,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H15" s="46" t="s">
         <v>0</v>
@@ -4565,49 +4602,51 @@
         <v>19</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K15" s="57" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="N15" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O15" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="P15" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q15" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R15" s="49">
+        <v>139</v>
+      </c>
+      <c r="O15" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="P15" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q15" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R15" s="47">
+        <v>2</v>
+      </c>
+      <c r="S15" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T15" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="S15" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="T15" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="U15" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="V15" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="W15" s="39"/>
-    </row>
-    <row r="16" spans="2:23" ht="42.75">
+      <c r="U15" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="V15" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="W15" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="2:23" ht="45">
       <c r="B16" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C16" s="46" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E16" s="46" t="s">
         <v>121</v>
@@ -4616,7 +4655,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H16" s="46" t="s">
         <v>8</v>
@@ -4625,43 +4664,45 @@
         <v>45</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="K16" s="57" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="N16" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="O16" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="P16" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q16" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="R16" s="48">
-        <v>0</v>
-      </c>
-      <c r="S16" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="T16" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="U16" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="V16" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="W16" s="66"/>
+        <v>139</v>
+      </c>
+      <c r="O16" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="P16" s="80" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q16" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="47">
+        <v>2</v>
+      </c>
+      <c r="S16" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T16" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="U16" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="V16" s="80" t="s">
+        <v>143</v>
+      </c>
+      <c r="W16" s="57" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="17" spans="2:23" ht="25.5">
       <c r="B17" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C17" s="46" t="s">
         <v>46</v>
@@ -4676,34 +4717,54 @@
         <v>1</v>
       </c>
       <c r="G17" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H17" s="46" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I17" s="46" t="s">
         <v>46</v>
       </c>
       <c r="J17" s="46" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="K17" s="58" t="s">
-        <v>168</v>
-      </c>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="48"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="39"/>
+        <v>161</v>
+      </c>
+      <c r="N17" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="O17" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="P17" s="80" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q17" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R17" s="47">
+        <v>1</v>
+      </c>
+      <c r="S17" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T17" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="U17" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="V17" s="80" t="s">
+        <v>141</v>
+      </c>
+      <c r="W17" s="58" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="18" spans="2:23">
       <c r="B18" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>92</v>
@@ -4718,36 +4779,56 @@
         <v>0</v>
       </c>
       <c r="G18" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K18" s="57" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="48"/>
-      <c r="S18" s="48"/>
-      <c r="T18" s="48"/>
-      <c r="U18" s="46"/>
-      <c r="V18" s="46"/>
-      <c r="W18" s="39"/>
+      <c r="N18" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="O18" s="80" t="s">
+        <v>92</v>
+      </c>
+      <c r="P18" s="80" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q18" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R18" s="49">
+        <v>0</v>
+      </c>
+      <c r="S18" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T18" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="U18" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="V18" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="W18" s="57" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="19" spans="2:23">
       <c r="B19" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C19" s="46" t="s">
         <v>88</v>
@@ -4762,42 +4843,62 @@
         <v>0</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J19" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K19" s="57" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="L19" s="38"/>
       <c r="M19" s="38"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="46"/>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="46"/>
-      <c r="V19" s="46"/>
-      <c r="W19" s="39"/>
+      <c r="N19" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="O19" s="80" t="s">
+        <v>88</v>
+      </c>
+      <c r="P19" s="80" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q19" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="R19" s="49">
+        <v>0</v>
+      </c>
+      <c r="S19" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="T19" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="U19" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="V19" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="W19" s="57" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="20" spans="2:23">
       <c r="B20" s="45" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C20" s="46" t="s">
         <v>89</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E20" s="46" t="s">
         <v>121</v>
@@ -4806,36 +4907,56 @@
         <v>0</v>
       </c>
       <c r="G20" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K20" s="57" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="L20" s="38"/>
       <c r="M20" s="38"/>
-      <c r="N20" s="46"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="48"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="48"/>
-      <c r="V20" s="48"/>
-      <c r="W20" s="39"/>
+      <c r="N20" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="O20" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="P20" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q20" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="R20" s="87">
+        <v>0</v>
+      </c>
+      <c r="S20" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="T20" s="82" t="s">
+        <v>145</v>
+      </c>
+      <c r="U20" s="82" t="s">
+        <v>145</v>
+      </c>
+      <c r="V20" s="82" t="s">
+        <v>145</v>
+      </c>
+      <c r="W20" s="59" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="21" spans="2:23">
       <c r="B21" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C21" s="46" t="s">
         <v>114</v>
@@ -4847,19 +4968,19 @@
         <v>121</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G21" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K21" s="57" t="s">
         <v>123</v>
@@ -4879,7 +5000,7 @@
     </row>
     <row r="22" spans="2:23">
       <c r="B22" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C22" s="46" t="s">
         <v>61</v>
@@ -4891,10 +5012,10 @@
         <v>121</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G22" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H22" s="48" t="s">
         <v>10</v>
@@ -4903,10 +5024,10 @@
         <v>61</v>
       </c>
       <c r="J22" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="K22" s="57" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="L22" s="38"/>
       <c r="M22" s="38"/>
@@ -4921,15 +5042,15 @@
       <c r="V22" s="48"/>
       <c r="W22" s="39"/>
     </row>
-    <row r="23" spans="2:23" ht="42.75">
+    <row r="23" spans="2:23" ht="45">
       <c r="B23" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C23" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E23" s="46" t="s">
         <v>121</v>
@@ -4938,7 +5059,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H23" s="48" t="s">
         <v>10</v>
@@ -4947,23 +5068,23 @@
         <v>23</v>
       </c>
       <c r="J23" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K23" s="57" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="L23" s="38"/>
       <c r="M23" s="38"/>
     </row>
     <row r="24" spans="2:23">
       <c r="B24" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C24" s="46" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E24" s="46" t="s">
         <v>121</v>
@@ -4972,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H24" s="48" t="s">
         <v>10</v>
@@ -4981,23 +5102,23 @@
         <v>27</v>
       </c>
       <c r="J24" s="48" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="K24" s="57" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="L24" s="38"/>
       <c r="M24" s="38"/>
     </row>
     <row r="25" spans="2:23">
       <c r="B25" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C25" s="46" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E25" s="46" t="s">
         <v>121</v>
@@ -5006,32 +5127,32 @@
         <v>1</v>
       </c>
       <c r="G25" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H25" s="48" t="s">
         <v>10</v>
       </c>
       <c r="I25" s="48" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="J25" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K25" s="57" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="L25" s="38"/>
       <c r="M25" s="38"/>
     </row>
-    <row r="26" spans="2:23" ht="42.75">
+    <row r="26" spans="2:23" ht="45">
       <c r="B26" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C26" s="46" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E26" s="46" t="s">
         <v>121</v>
@@ -5040,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H26" s="48" t="s">
         <v>10</v>
@@ -5049,23 +5170,25 @@
         <v>29</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K26" s="57" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="L26" s="38"/>
       <c r="M26" s="38"/>
+      <c r="R26" s="89"/>
+      <c r="S26" s="89"/>
     </row>
     <row r="27" spans="2:23">
       <c r="B27" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C27" s="46" t="s">
         <v>30</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E27" s="46" t="s">
         <v>121</v>
@@ -5074,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H27" s="48" t="s">
         <v>10</v>
@@ -5083,23 +5206,23 @@
         <v>30</v>
       </c>
       <c r="J27" s="46" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K27" s="57" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="L27" s="38"/>
       <c r="M27" s="38"/>
     </row>
     <row r="28" spans="2:23">
       <c r="B28" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C28" s="46" t="s">
         <v>31</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E28" s="46" t="s">
         <v>121</v>
@@ -5108,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H28" s="48" t="s">
         <v>10</v>
@@ -5117,23 +5240,23 @@
         <v>31</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K28" s="58" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="L28" s="38"/>
       <c r="M28" s="38"/>
     </row>
-    <row r="29" spans="2:23" ht="28.5">
+    <row r="29" spans="2:23" ht="30">
       <c r="B29" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C29" s="46" t="s">
         <v>33</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E29" s="46" t="s">
         <v>121</v>
@@ -5142,7 +5265,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H29" s="48" t="s">
         <v>11</v>
@@ -5151,23 +5274,23 @@
         <v>33</v>
       </c>
       <c r="J29" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K29" s="57" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="L29" s="38"/>
       <c r="M29" s="38"/>
     </row>
-    <row r="30" spans="2:23" ht="28.5">
+    <row r="30" spans="2:23" ht="30">
       <c r="B30" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C30" s="46" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E30" s="46" t="s">
         <v>121</v>
@@ -5176,7 +5299,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H30" s="48" t="s">
         <v>11</v>
@@ -5185,23 +5308,23 @@
         <v>34</v>
       </c>
       <c r="J30" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K30" s="57" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="L30" s="38"/>
       <c r="M30" s="38"/>
     </row>
-    <row r="31" spans="2:23" ht="28.5">
+    <row r="31" spans="2:23" ht="30">
       <c r="B31" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C31" s="46" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E31" s="46" t="s">
         <v>121</v>
@@ -5210,7 +5333,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H31" s="48" t="s">
         <v>11</v>
@@ -5219,23 +5342,23 @@
         <v>35</v>
       </c>
       <c r="J31" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K31" s="57" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="L31" s="38"/>
       <c r="M31" s="38"/>
     </row>
-    <row r="32" spans="2:23" ht="28.5">
+    <row r="32" spans="2:23" ht="30">
       <c r="B32" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C32" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E32" s="46" t="s">
         <v>121</v>
@@ -5244,7 +5367,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H32" s="48" t="s">
         <v>11</v>
@@ -5253,23 +5376,23 @@
         <v>36</v>
       </c>
       <c r="J32" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K32" s="57" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L32" s="38"/>
       <c r="M32" s="38"/>
     </row>
-    <row r="33" spans="2:13" ht="28.5">
+    <row r="33" spans="2:13" ht="30">
       <c r="B33" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C33" s="46" t="s">
         <v>38</v>
       </c>
       <c r="D33" s="46" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E33" s="46" t="s">
         <v>121</v>
@@ -5278,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H33" s="48" t="s">
         <v>11</v>
@@ -5287,17 +5410,17 @@
         <v>38</v>
       </c>
       <c r="J33" s="48" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="K33" s="57" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="L33" s="38"/>
       <c r="M33" s="38"/>
     </row>
-    <row r="34" spans="2:13" ht="28.5">
+    <row r="34" spans="2:13" ht="30">
       <c r="B34" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C34" s="46" t="s">
         <v>39</v>
@@ -5312,7 +5435,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H34" s="48" t="s">
         <v>11</v>
@@ -5324,20 +5447,20 @@
         <v>120</v>
       </c>
       <c r="K34" s="57" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="L34" s="38"/>
       <c r="M34" s="38"/>
     </row>
-    <row r="35" spans="2:13" ht="28.5">
+    <row r="35" spans="2:13" ht="30">
       <c r="B35" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C35" s="46" t="s">
         <v>40</v>
       </c>
       <c r="D35" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E35" s="46" t="s">
         <v>121</v>
@@ -5346,7 +5469,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H35" s="48" t="s">
         <v>11</v>
@@ -5355,23 +5478,23 @@
         <v>40</v>
       </c>
       <c r="J35" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="K35" s="57" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="L35" s="38"/>
       <c r="M35" s="38"/>
     </row>
-    <row r="36" spans="2:13" ht="28.5">
+    <row r="36" spans="2:13" ht="30">
       <c r="B36" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C36" s="46" t="s">
         <v>41</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E36" s="46" t="s">
         <v>121</v>
@@ -5380,7 +5503,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H36" s="48" t="s">
         <v>11</v>
@@ -5389,23 +5512,23 @@
         <v>41</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K36" s="57" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="L36" s="38"/>
       <c r="M36" s="38"/>
     </row>
     <row r="37" spans="2:13" ht="32.25" customHeight="1">
       <c r="B37" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C37" s="46" t="s">
         <v>90</v>
       </c>
       <c r="D37" s="46" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E37" s="46" t="s">
         <v>121</v>
@@ -5414,32 +5537,32 @@
         <v>2</v>
       </c>
       <c r="G37" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H37" s="48" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I37" s="48" t="s">
         <v>23</v>
       </c>
       <c r="J37" s="48" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K37" s="57" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="L37" s="38"/>
       <c r="M37" s="38"/>
     </row>
-    <row r="38" spans="2:13" ht="28.5">
+    <row r="38" spans="2:13" ht="30">
       <c r="B38" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C38" s="46" t="s">
         <v>91</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E38" s="46" t="s">
         <v>121</v>
@@ -5448,32 +5571,32 @@
         <v>2</v>
       </c>
       <c r="G38" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H38" s="48" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I38" s="48" t="s">
         <v>48</v>
       </c>
       <c r="J38" s="48" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K38" s="57" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L38" s="38"/>
       <c r="M38" s="38"/>
     </row>
-    <row r="39" spans="2:13" ht="28.5">
+    <row r="39" spans="2:13" ht="30">
       <c r="B39" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C39" s="46" t="s">
         <v>50</v>
       </c>
       <c r="D39" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E39" s="46" t="s">
         <v>121</v>
@@ -5482,26 +5605,26 @@
         <v>2</v>
       </c>
       <c r="G39" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H39" s="48" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I39" s="48" t="s">
         <v>50</v>
       </c>
       <c r="J39" s="48" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="K39" s="57" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L39" s="38"/>
       <c r="M39" s="38"/>
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C40" s="46" t="s">
         <v>92</v>
@@ -5516,26 +5639,26 @@
         <v>0</v>
       </c>
       <c r="G40" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K40" s="57" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="L40" s="38"/>
       <c r="M40" s="38"/>
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C41" s="46" t="s">
         <v>88</v>
@@ -5550,32 +5673,32 @@
         <v>0</v>
       </c>
       <c r="G41" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K41" s="57" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="L41" s="38"/>
       <c r="M41" s="38"/>
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C42" s="46" t="s">
         <v>89</v>
       </c>
       <c r="D42" s="46" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E42" s="46" t="s">
         <v>121</v>
@@ -5584,19 +5707,19 @@
         <v>0</v>
       </c>
       <c r="G42" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K42" s="57" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="L42" s="38"/>
       <c r="M42" s="38"/>
@@ -5614,23 +5737,23 @@
       <c r="E43" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="F43" s="53" t="s">
-        <v>152</v>
+      <c r="F43" s="49">
+        <v>0</v>
       </c>
       <c r="G43" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K43" s="57" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L43" s="38"/>
       <c r="M43" s="38"/>
@@ -5652,19 +5775,19 @@
         <v>0</v>
       </c>
       <c r="G44" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K44" s="57" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="2:13">
@@ -5684,27 +5807,25 @@
         <v>0</v>
       </c>
       <c r="G45" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K45" s="57" t="s">
-        <v>127</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="K45" s="57"/>
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="45" t="s">
         <v>119</v>
       </c>
       <c r="C46" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D46" s="46" t="s">
         <v>120</v>
@@ -5716,30 +5837,28 @@
         <v>0</v>
       </c>
       <c r="G46" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K46" s="57" t="s">
-        <v>129</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="K46" s="57"/>
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="45" t="s">
         <v>119</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E47" s="46" t="s">
         <v>121</v>
@@ -5748,27 +5867,25 @@
         <v>0</v>
       </c>
       <c r="G47" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J47" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K47" s="57" t="s">
-        <v>131</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="K47" s="57"/>
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="45" t="s">
         <v>119</v>
       </c>
       <c r="C48" s="46" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D48" s="46" t="s">
         <v>120</v>
@@ -5780,27 +5897,25 @@
         <v>0</v>
       </c>
       <c r="G48" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K48" s="57" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
+        <v>145</v>
+      </c>
+      <c r="K48" s="57"/>
+    </row>
+    <row r="49" spans="2:14">
       <c r="B49" s="45" t="s">
         <v>119</v>
       </c>
       <c r="C49" s="46" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D49" s="46" t="s">
         <v>120</v>
@@ -5812,27 +5927,25 @@
         <v>0</v>
       </c>
       <c r="G49" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J49" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K49" s="57" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
+        <v>145</v>
+      </c>
+      <c r="K49" s="57"/>
+    </row>
+    <row r="50" spans="2:14">
       <c r="B50" s="45" t="s">
         <v>119</v>
       </c>
       <c r="C50" s="46" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>120</v>
@@ -5844,30 +5957,28 @@
         <v>0</v>
       </c>
       <c r="G50" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K50" s="57" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
+        <v>145</v>
+      </c>
+      <c r="K50" s="57"/>
+    </row>
+    <row r="51" spans="2:14">
       <c r="B51" s="45" t="s">
         <v>119</v>
       </c>
       <c r="C51" s="46" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D51" s="46" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="E51" s="46" t="s">
         <v>121</v>
@@ -5876,126 +5987,122 @@
         <v>0</v>
       </c>
       <c r="G51" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J51" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K51" s="57" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
+        <v>145</v>
+      </c>
+      <c r="K51" s="57"/>
+    </row>
+    <row r="52" spans="2:14">
       <c r="B52" s="45" t="s">
-        <v>204</v>
+        <v>119</v>
       </c>
       <c r="C52" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="E52" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F52" s="49">
+        <v>0</v>
+      </c>
+      <c r="G52" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="H52" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="I52" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="J52" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K52" s="57"/>
+    </row>
+    <row r="53" spans="2:14">
+      <c r="B53" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="D52" s="46" t="s">
+      <c r="D53" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E52" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="F52" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="G52" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="J52" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K52" s="57" t="s">
+      <c r="E53" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F53" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G53" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="H53" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="I53" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="J53" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K53" s="57" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="C53" s="46" t="s">
+    <row r="54" spans="2:14">
+      <c r="B54" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="D53" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="E53" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="F53" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="G53" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="H53" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="I53" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="J53" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="K53" s="57" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" ht="42.75">
-      <c r="B54" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="C54" s="46" t="s">
-        <v>52</v>
-      </c>
       <c r="D54" s="46" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="E54" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="F54" s="49">
-        <v>1</v>
+      <c r="F54" s="50" t="s">
+        <v>145</v>
       </c>
       <c r="G54" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H54" s="48" t="s">
         <v>3</v>
       </c>
       <c r="I54" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="J54" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="K54" s="57" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" ht="45">
+      <c r="B55" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C55" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="J54" s="46" t="s">
-        <v>205</v>
-      </c>
-      <c r="K54" s="57" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="B55" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="C55" s="46" t="s">
-        <v>53</v>
-      </c>
       <c r="D55" s="46" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="E55" s="46" t="s">
         <v>121</v>
@@ -6004,59 +6111,59 @@
         <v>1</v>
       </c>
       <c r="G55" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H55" s="48" t="s">
         <v>3</v>
       </c>
       <c r="I55" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="J55" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="K55" s="57" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14">
+      <c r="B56" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="J55" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="K55" s="57" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C56" s="46" t="s">
+      <c r="D56" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F56" s="49">
+        <v>1</v>
+      </c>
+      <c r="G56" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H56" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="J56" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="K56" s="57" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14">
+      <c r="B57" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" s="46" t="s">
         <v>94</v>
-      </c>
-      <c r="D56" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="E56" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="F56" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="G56" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="J56" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K56" s="57" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C57" s="46" t="s">
-        <v>54</v>
       </c>
       <c r="D57" s="46" t="s">
         <v>120</v>
@@ -6064,66 +6171,66 @@
       <c r="E57" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="F57" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="G57" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="H57" s="48" t="s">
+      <c r="F57" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G57" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K57" s="57" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14">
+      <c r="B58" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E58" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F58" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G58" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H58" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I57" s="46" t="s">
+      <c r="I58" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="J57" s="46" t="s">
+      <c r="J58" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="K57" s="57" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" ht="28.5">
-      <c r="B58" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C58" s="46" t="s">
+      <c r="K58" s="57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" ht="45">
+      <c r="B59" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C59" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="F58" s="49">
-        <v>2</v>
-      </c>
-      <c r="G58" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="H58" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="I58" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="J58" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="K58" s="57" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11" ht="28.5">
-      <c r="B59" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C59" s="46" t="s">
-        <v>91</v>
-      </c>
       <c r="D59" s="46" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E59" s="46" t="s">
         <v>121</v>
@@ -6132,30 +6239,30 @@
         <v>2</v>
       </c>
       <c r="G59" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H59" s="48" t="s">
         <v>2</v>
       </c>
       <c r="I59" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="J59" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="K59" s="57" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" ht="45">
+      <c r="B60" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="J59" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="K59" s="57" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11" ht="28.5">
-      <c r="B60" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C60" s="46" t="s">
-        <v>50</v>
-      </c>
       <c r="D60" s="46" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="E60" s="46" t="s">
         <v>121</v>
@@ -6164,94 +6271,95 @@
         <v>2</v>
       </c>
       <c r="G60" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H60" s="48" t="s">
         <v>2</v>
       </c>
       <c r="I60" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="J60" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="K60" s="57" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" ht="45">
+      <c r="B61" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C61" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="J60" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="K60" s="57" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C61" s="46" t="s">
+      <c r="D61" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F61" s="49">
+        <v>2</v>
+      </c>
+      <c r="G61" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H61" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I61" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="J61" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="K61" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="N61" s="89"/>
+    </row>
+    <row r="62" spans="2:14">
+      <c r="B62" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C62" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="E61" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="F61" s="49">
+      <c r="D62" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="E62" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F62" s="49">
         <v>0</v>
       </c>
-      <c r="G61" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="H61" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="I61" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="J61" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="K61" s="57" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C62" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="D62" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="E62" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="F62" s="49">
-        <v>1</v>
-      </c>
       <c r="G62" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H62" s="48" t="s">
         <v>4</v>
       </c>
       <c r="I62" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="J62" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="K62" s="57" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14">
+      <c r="B63" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="J62" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="K62" s="57" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C63" s="46" t="s">
-        <v>56</v>
-      </c>
       <c r="D63" s="46" t="s">
-        <v>120</v>
+        <v>271</v>
       </c>
       <c r="E63" s="46" t="s">
         <v>121</v>
@@ -6260,30 +6368,30 @@
         <v>1</v>
       </c>
       <c r="G63" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H63" s="48" t="s">
         <v>4</v>
       </c>
       <c r="I63" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="K63" s="57" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14">
+      <c r="B64" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="J63" s="46" t="s">
+      <c r="D64" s="46" t="s">
         <v>120</v>
-      </c>
-      <c r="K63" s="57" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="C64" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="D64" s="46" t="s">
-        <v>206</v>
       </c>
       <c r="E64" s="46" t="s">
         <v>121</v>
@@ -6292,30 +6400,30 @@
         <v>1</v>
       </c>
       <c r="G64" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H64" s="48" t="s">
         <v>4</v>
       </c>
       <c r="I64" s="46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J64" s="46" t="s">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="K64" s="57" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="2:11">
       <c r="B65" s="45" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C65" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D65" s="46" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="E65" s="46" t="s">
         <v>121</v>
@@ -6324,59 +6432,59 @@
         <v>1</v>
       </c>
       <c r="G65" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H65" s="48" t="s">
         <v>4</v>
       </c>
       <c r="I65" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J65" s="46" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="K65" s="57" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" spans="2:11">
       <c r="B66" s="45" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C66" s="46" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="E66" s="46" t="s">
         <v>121</v>
       </c>
       <c r="F66" s="49">
-        <v>0</v>
-      </c>
-      <c r="G66" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I66" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="J66" s="37" t="s">
-        <v>152</v>
+        <v>1</v>
+      </c>
+      <c r="G66" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H66" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="J66" s="46" t="s">
+        <v>143</v>
       </c>
       <c r="K66" s="57" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="2:11">
       <c r="B67" s="45" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C67" s="46" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D67" s="46" t="s">
         <v>125</v>
@@ -6388,91 +6496,91 @@
         <v>0</v>
       </c>
       <c r="G67" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J67" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K67" s="57" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="2:11">
       <c r="B68" s="45" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C68" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D68" s="46" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E68" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="F68" s="48">
+      <c r="F68" s="49">
         <v>0</v>
       </c>
-      <c r="G68" s="37" t="s">
-        <v>152</v>
+      <c r="G68" s="53" t="s">
+        <v>145</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K68" s="57" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="2:11">
       <c r="B69" s="45" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C69" s="46" t="s">
-        <v>188</v>
+        <v>89</v>
       </c>
       <c r="D69" s="46" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E69" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="F69" s="37" t="s">
-        <v>152</v>
+      <c r="F69" s="49">
+        <v>0</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I69" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J69" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K69" s="57" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="2:11">
       <c r="B70" s="45" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C70" s="46" t="s">
-        <v>276</v>
+        <v>181</v>
       </c>
       <c r="D70" s="46" t="s">
         <v>120</v>
@@ -6481,63 +6589,63 @@
         <v>121</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K70" s="57"/>
-    </row>
-    <row r="71" spans="2:11" ht="28.5">
+        <v>145</v>
+      </c>
+      <c r="K70" s="57" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
       <c r="B71" s="45" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C71" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="D71" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E71" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F71" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="G71" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K71" s="57"/>
+    </row>
+    <row r="72" spans="2:11" ht="30">
+      <c r="B72" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="C72" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="D71" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="E71" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="F71" s="48">
-        <v>2</v>
-      </c>
-      <c r="G71" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="H71" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="I71" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="J71" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="K71" s="57" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="45" t="s">
-        <v>187</v>
-      </c>
-      <c r="C72" s="46" t="s">
-        <v>91</v>
-      </c>
       <c r="D72" s="46" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E72" s="46" t="s">
         <v>121</v>
@@ -6546,62 +6654,62 @@
         <v>2</v>
       </c>
       <c r="G72" s="48" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H72" s="48" t="s">
         <v>2</v>
       </c>
       <c r="I72" s="48" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="J72" s="46" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K72" s="57" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" ht="28.5">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
       <c r="B73" s="45" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C73" s="46" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="D73" s="46" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="E73" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="F73" s="49">
+      <c r="F73" s="48">
         <v>2</v>
       </c>
-      <c r="G73" s="54" t="s">
-        <v>147</v>
+      <c r="G73" s="48" t="s">
+        <v>140</v>
       </c>
       <c r="H73" s="48" t="s">
         <v>2</v>
       </c>
       <c r="I73" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="J73" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="K73" s="57" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" ht="30">
+      <c r="B74" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="C74" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="J73" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="K73" s="57" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="45" t="s">
-        <v>187</v>
-      </c>
-      <c r="C74" s="46" t="s">
-        <v>66</v>
-      </c>
       <c r="D74" s="46" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="E74" s="46" t="s">
         <v>121</v>
@@ -6610,30 +6718,30 @@
         <v>2</v>
       </c>
       <c r="G74" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H74" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="I74" s="46" t="s">
-        <v>66</v>
+        <v>2</v>
+      </c>
+      <c r="I74" s="48" t="s">
+        <v>50</v>
       </c>
       <c r="J74" s="46" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="K74" s="57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="75" spans="2:11">
       <c r="B75" s="45" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C75" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D75" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E75" s="46" t="s">
         <v>121</v>
@@ -6642,30 +6750,30 @@
         <v>2</v>
       </c>
       <c r="G75" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H75" s="48" t="s">
         <v>5</v>
       </c>
       <c r="I75" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J75" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K75" s="57" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="2:11">
       <c r="B76" s="45" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C76" s="46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D76" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E76" s="46" t="s">
         <v>121</v>
@@ -6674,30 +6782,30 @@
         <v>2</v>
       </c>
       <c r="G76" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H76" s="48" t="s">
         <v>5</v>
       </c>
       <c r="I76" s="46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J76" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K76" s="57" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="2:11">
       <c r="B77" s="45" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C77" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D77" s="46" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E77" s="46" t="s">
         <v>121</v>
@@ -6706,59 +6814,59 @@
         <v>2</v>
       </c>
       <c r="G77" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H77" s="48" t="s">
         <v>5</v>
       </c>
       <c r="I77" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="J77" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="K77" s="57" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" ht="30">
+      <c r="B78" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="C78" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="J77" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="K77" s="57" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="C78" s="46" t="s">
-        <v>246</v>
-      </c>
       <c r="D78" s="46" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="E78" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="F78" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G78" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="H78" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I78" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="J78" s="37" t="s">
-        <v>152</v>
+      <c r="F78" s="49">
+        <v>2</v>
+      </c>
+      <c r="G78" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H78" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I78" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="J78" s="46" t="s">
+        <v>144</v>
       </c>
       <c r="K78" s="57" t="s">
-        <v>123</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="45" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="D79" s="46" t="s">
         <v>120</v>
@@ -6767,65 +6875,65 @@
         <v>121</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G79" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="H79" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="I79" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="G79" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="H79" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="I79" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="J79" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K79" s="57" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="C80" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="J79" s="46" t="s">
+      <c r="D80" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="K79" s="57" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" ht="42.75">
-      <c r="B80" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="C80" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="D80" s="46" t="s">
-        <v>210</v>
-      </c>
       <c r="E80" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="F80" s="49">
-        <v>1</v>
+      <c r="F80" s="37" t="s">
+        <v>145</v>
       </c>
       <c r="G80" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H80" s="48" t="s">
         <v>12</v>
       </c>
       <c r="I80" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="J80" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="K80" s="57" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" ht="45">
+      <c r="B81" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="C81" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="J80" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="K80" s="57" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11" ht="42.75">
-      <c r="B81" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="C81" s="46" t="s">
-        <v>76</v>
-      </c>
       <c r="D81" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E81" s="46" t="s">
         <v>121</v>
@@ -6834,30 +6942,30 @@
         <v>1</v>
       </c>
       <c r="G81" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H81" s="48" t="s">
         <v>12</v>
       </c>
       <c r="I81" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="K81" s="57" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" ht="45">
+      <c r="B82" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="J81" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="K81" s="57" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="C82" s="46" t="s">
-        <v>77</v>
-      </c>
       <c r="D82" s="46" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="E82" s="46" t="s">
         <v>121</v>
@@ -6866,30 +6974,30 @@
         <v>1</v>
       </c>
       <c r="G82" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H82" s="48" t="s">
         <v>12</v>
       </c>
       <c r="I82" s="46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J82" s="46" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="K82" s="57" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="45" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C83" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D83" s="46" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E83" s="46" t="s">
         <v>121</v>
@@ -6898,27 +7006,27 @@
         <v>1</v>
       </c>
       <c r="G83" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H83" s="48" t="s">
         <v>12</v>
       </c>
       <c r="I83" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J83" s="46" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="K83" s="57" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="84" spans="2:11">
       <c r="B84" s="45" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C84" s="46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D84" s="46" t="s">
         <v>120</v>
@@ -6930,83 +7038,83 @@
         <v>1</v>
       </c>
       <c r="G84" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H84" s="48" t="s">
         <v>12</v>
       </c>
       <c r="I84" s="46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J84" s="46" t="s">
         <v>120</v>
       </c>
       <c r="K84" s="57" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11" ht="28.5">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
       <c r="B85" s="45" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="C85" s="46" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="D85" s="46" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E85" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="F85" s="50" t="s">
-        <v>152</v>
+        <v>121</v>
+      </c>
+      <c r="F85" s="49">
+        <v>1</v>
       </c>
       <c r="G85" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H85" s="48" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I85" s="46" t="s">
-        <v>255</v>
-      </c>
-      <c r="J85" s="48" t="s">
-        <v>125</v>
+        <v>79</v>
+      </c>
+      <c r="J85" s="46" t="s">
+        <v>120</v>
       </c>
       <c r="K85" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" ht="30">
       <c r="B86" s="45" t="s">
         <v>97</v>
       </c>
       <c r="C86" s="46" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D86" s="46" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E86" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G86" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H86" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="I86" s="48" t="s">
-        <v>54</v>
+      <c r="I86" s="46" t="s">
+        <v>248</v>
       </c>
       <c r="J86" s="48" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K86" s="57" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
     </row>
     <row r="87" spans="2:11">
@@ -7014,31 +7122,31 @@
         <v>97</v>
       </c>
       <c r="C87" s="46" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D87" s="46" t="s">
         <v>120</v>
       </c>
       <c r="E87" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G87" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H87" s="48" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="I87" s="48" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J87" s="48" t="s">
         <v>120</v>
       </c>
       <c r="K87" s="57" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="88" spans="2:11">
@@ -7046,31 +7154,31 @@
         <v>97</v>
       </c>
       <c r="C88" s="46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D88" s="46" t="s">
         <v>120</v>
       </c>
       <c r="E88" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F88" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G88" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H88" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="I88" s="46" t="s">
-        <v>61</v>
+        <v>242</v>
+      </c>
+      <c r="I88" s="48" t="s">
+        <v>42</v>
       </c>
       <c r="J88" s="48" t="s">
         <v>120</v>
       </c>
       <c r="K88" s="57" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" spans="2:11">
@@ -7078,31 +7186,31 @@
         <v>97</v>
       </c>
       <c r="C89" s="46" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D89" s="46" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E89" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F89" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G89" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H89" s="48" t="s">
         <v>5</v>
       </c>
       <c r="I89" s="46" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="J89" s="48" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="K89" s="57" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="90" spans="2:11">
@@ -7110,31 +7218,31 @@
         <v>97</v>
       </c>
       <c r="C90" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="D90" s="48" t="s">
-        <v>120</v>
+        <v>93</v>
+      </c>
+      <c r="D90" s="46" t="s">
+        <v>173</v>
       </c>
       <c r="E90" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F90" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G90" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H90" s="48" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="I90" s="46" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="J90" s="48" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="K90" s="57" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="91" spans="2:11">
@@ -7142,31 +7250,31 @@
         <v>97</v>
       </c>
       <c r="C91" s="46" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="D91" s="48" t="s">
         <v>120</v>
       </c>
       <c r="E91" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F91" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G91" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H91" s="48" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I91" s="46" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="J91" s="48" t="s">
         <v>120</v>
       </c>
       <c r="K91" s="57" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="2:11">
@@ -7174,31 +7282,31 @@
         <v>97</v>
       </c>
       <c r="C92" s="46" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D92" s="48" t="s">
         <v>120</v>
       </c>
       <c r="E92" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F92" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G92" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H92" s="48" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I92" s="46" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="J92" s="48" t="s">
         <v>120</v>
       </c>
       <c r="K92" s="57" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" spans="2:11">
@@ -7206,31 +7314,31 @@
         <v>97</v>
       </c>
       <c r="C93" s="46" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D93" s="48" t="s">
         <v>120</v>
       </c>
       <c r="E93" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F93" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G93" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H93" s="48" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I93" s="46" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J93" s="48" t="s">
         <v>120</v>
       </c>
       <c r="K93" s="57" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="94" spans="2:11">
@@ -7238,319 +7346,351 @@
         <v>97</v>
       </c>
       <c r="C94" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="D94" s="46" t="s">
-        <v>248</v>
+        <v>100</v>
+      </c>
+      <c r="D94" s="48" t="s">
+        <v>120</v>
       </c>
       <c r="E94" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G94" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H94" s="48" t="s">
-        <v>249</v>
-      </c>
-      <c r="I94" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="J94" s="46" t="s">
-        <v>248</v>
+        <v>242</v>
+      </c>
+      <c r="I94" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="J94" s="48" t="s">
+        <v>120</v>
       </c>
       <c r="K94" s="57" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11" ht="30" customHeight="1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
       <c r="B95" s="45" t="s">
         <v>97</v>
       </c>
       <c r="C95" s="46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D95" s="46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E95" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F95" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G95" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H95" s="48" t="s">
-        <v>250</v>
-      </c>
-      <c r="I95" s="46" t="s">
-        <v>71</v>
+        <v>242</v>
+      </c>
+      <c r="I95" s="48" t="s">
+        <v>75</v>
       </c>
       <c r="J95" s="46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="K95" s="57" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11" ht="42.75">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" ht="30" customHeight="1">
       <c r="B96" s="45" t="s">
         <v>97</v>
       </c>
       <c r="C96" s="46" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D96" s="46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E96" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G96" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H96" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I96" s="46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J96" s="46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="K96" s="57" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11" ht="42.75">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" ht="45">
       <c r="B97" s="45" t="s">
         <v>97</v>
       </c>
       <c r="C97" s="46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D97" s="46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E97" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F97" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G97" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="H97" s="46" t="s">
-        <v>251</v>
+        <v>140</v>
+      </c>
+      <c r="H97" s="48" t="s">
+        <v>243</v>
       </c>
       <c r="I97" s="46" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J97" s="46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="K97" s="57" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11" ht="85.5">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" ht="45">
       <c r="B98" s="45" t="s">
         <v>97</v>
       </c>
       <c r="C98" s="46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D98" s="46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E98" s="46" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F98" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G98" s="54" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H98" s="46" t="s">
-        <v>252</v>
-      </c>
-      <c r="I98" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="J98" s="37" t="s">
-        <v>152</v>
+        <v>244</v>
+      </c>
+      <c r="I98" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="J98" s="46" t="s">
+        <v>241</v>
       </c>
       <c r="K98" s="57" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11" ht="128.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11" ht="90">
       <c r="B99" s="45" t="s">
         <v>97</v>
       </c>
       <c r="C99" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D99" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="E99" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="F99" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G99" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H99" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="I99" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="J99" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K99" s="57" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" ht="150">
+      <c r="B100" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="D99" s="46" t="s">
-        <v>248</v>
-      </c>
-      <c r="E99" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="F99" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="G99" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="H99" s="48" t="s">
+      <c r="D100" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="E100" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="F100" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G100" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H100" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="I100" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="J100" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K100" s="57" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" ht="30">
+      <c r="B101" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="C101" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D101" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E101" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="F101" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G101" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="H101" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="I101" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="J101" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="K101" s="57" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" ht="30">
+      <c r="B102" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="C102" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="D102" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E102" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="F102" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G102" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="H102" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="I102" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="J102" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="K102" s="57" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="C103" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="D103" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E103" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="F103" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G103" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="H103" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="I103" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="J103" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="K103" s="57" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="C104" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="D104" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="E104" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="F104" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="G104" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="H104" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="I104" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="J104" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="K104" s="59" t="s">
         <v>267</v>
-      </c>
-      <c r="I99" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="J99" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K99" s="57" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11" ht="28.5">
-      <c r="B100" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="C100" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="D100" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="E100" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="F100" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="G100" s="54" t="s">
-        <v>277</v>
-      </c>
-      <c r="H100" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="I100" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="J100" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="K100" s="57" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11">
-      <c r="B101" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="C101" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="D101" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="E101" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="F101" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="G101" s="54" t="s">
-        <v>277</v>
-      </c>
-      <c r="H101" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="I101" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="J101" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="K101" s="57" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11">
-      <c r="B102" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="C102" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="D102" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="E102" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="F102" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="G102" s="54" t="s">
-        <v>277</v>
-      </c>
-      <c r="H102" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="I102" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="J102" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="K102" s="57" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11">
-      <c r="B103" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="C103" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="D103" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="E103" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="F103" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="G103" s="56" t="s">
-        <v>277</v>
-      </c>
-      <c r="H103" s="52" t="s">
-        <v>269</v>
-      </c>
-      <c r="I103" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="J103" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="K103" s="59" t="s">
-        <v>274</v>
       </c>
     </row>
   </sheetData>
